--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -3548,10 +3548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119548728</v>
+        <v>119548779</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,25 +3560,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480559</v>
+        <v>480282</v>
       </c>
       <c r="R29" t="n">
-        <v>6826033</v>
+        <v>6826360</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119548779</v>
+        <v>119548744</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480282</v>
+        <v>480408</v>
       </c>
       <c r="R30" t="n">
-        <v>6826360</v>
+        <v>6826259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119548744</v>
+        <v>119548728</v>
       </c>
       <c r="B31" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,25 +3764,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480408</v>
+        <v>480559</v>
       </c>
       <c r="R31" t="n">
-        <v>6826259</v>
+        <v>6826033</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119548983</v>
+        <v>119548593</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480586</v>
+        <v>480302</v>
       </c>
       <c r="R40" t="n">
-        <v>6826020</v>
+        <v>6826281</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119548593</v>
+        <v>119548983</v>
       </c>
       <c r="B41" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480302</v>
+        <v>480586</v>
       </c>
       <c r="R41" t="n">
-        <v>6826281</v>
+        <v>6826020</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548641</v>
+        <v>119548749</v>
       </c>
       <c r="B62" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480602</v>
+        <v>480500</v>
       </c>
       <c r="R62" t="n">
-        <v>6826129</v>
+        <v>6826126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7061,10 +7061,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548649</v>
+        <v>119548758</v>
       </c>
       <c r="B63" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7077,21 +7077,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7101,10 +7101,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480632</v>
+        <v>480401</v>
       </c>
       <c r="R63" t="n">
-        <v>6826029</v>
+        <v>6826229</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7163,10 +7163,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548749</v>
+        <v>119548641</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7179,21 +7179,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480500</v>
+        <v>480602</v>
       </c>
       <c r="R64" t="n">
-        <v>6826126</v>
+        <v>6826129</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7265,10 +7265,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548758</v>
+        <v>119548649</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7281,21 +7281,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480401</v>
+        <v>480632</v>
       </c>
       <c r="R65" t="n">
-        <v>6826229</v>
+        <v>6826029</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119548772</v>
+        <v>119548677</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480202</v>
+        <v>480500</v>
       </c>
       <c r="R75" t="n">
-        <v>6826368</v>
+        <v>6826126</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119548959</v>
+        <v>119548730</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8417,47 +8417,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480651</v>
+        <v>480608</v>
       </c>
       <c r="R76" t="n">
-        <v>6826110</v>
+        <v>6826130</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8720,10 +8711,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119548677</v>
+        <v>119548772</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8736,21 +8727,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8760,10 +8751,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480500</v>
+        <v>480202</v>
       </c>
       <c r="R79" t="n">
-        <v>6826126</v>
+        <v>6826368</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8822,10 +8813,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548730</v>
+        <v>119548959</v>
       </c>
       <c r="B80" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8834,38 +8825,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480608</v>
+        <v>480651</v>
       </c>
       <c r="R80" t="n">
-        <v>6826130</v>
+        <v>6826110</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119549030</v>
+        <v>119548706</v>
       </c>
       <c r="B89" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9756,21 +9756,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9780,10 +9780,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480568</v>
+        <v>480635</v>
       </c>
       <c r="R89" t="n">
-        <v>6826020</v>
+        <v>6826136</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119549025</v>
+        <v>119549030</v>
       </c>
       <c r="B90" t="n">
         <v>78171</v>
@@ -9882,10 +9882,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480604</v>
+        <v>480568</v>
       </c>
       <c r="R90" t="n">
-        <v>6826016</v>
+        <v>6826020</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9944,10 +9944,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119548648</v>
+        <v>119549025</v>
       </c>
       <c r="B91" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480609</v>
+        <v>480604</v>
       </c>
       <c r="R91" t="n">
-        <v>6826065</v>
+        <v>6826016</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548594</v>
+        <v>119548648</v>
       </c>
       <c r="B92" t="n">
         <v>78560</v>
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480261</v>
+        <v>480609</v>
       </c>
       <c r="R92" t="n">
-        <v>6826289</v>
+        <v>6826065</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10148,10 +10148,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119549026</v>
+        <v>119548594</v>
       </c>
       <c r="B93" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10164,21 +10164,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10188,10 +10188,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480579</v>
+        <v>480261</v>
       </c>
       <c r="R93" t="n">
-        <v>6826019</v>
+        <v>6826289</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119548974</v>
+        <v>119549026</v>
       </c>
       <c r="B94" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10262,47 +10262,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480211</v>
+        <v>480579</v>
       </c>
       <c r="R94" t="n">
-        <v>6826353</v>
+        <v>6826019</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10361,10 +10352,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119548722</v>
+        <v>119548974</v>
       </c>
       <c r="B95" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10377,26 +10368,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10410,10 +10401,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480236</v>
+        <v>480211</v>
       </c>
       <c r="R95" t="n">
-        <v>6826375</v>
+        <v>6826353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,10 +10463,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119548767</v>
+        <v>119548722</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10484,38 +10475,47 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480266</v>
+        <v>480236</v>
       </c>
       <c r="R96" t="n">
-        <v>6826294</v>
+        <v>6826375</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119548776</v>
+        <v>119548767</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480250</v>
+        <v>480266</v>
       </c>
       <c r="R97" t="n">
-        <v>6826379</v>
+        <v>6826294</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119548762</v>
+        <v>119548776</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480309</v>
+        <v>480250</v>
       </c>
       <c r="R98" t="n">
-        <v>6826277</v>
+        <v>6826379</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119548682</v>
+        <v>119548762</v>
       </c>
       <c r="B99" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10794,21 +10794,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480635</v>
+        <v>480309</v>
       </c>
       <c r="R99" t="n">
-        <v>6826107</v>
+        <v>6826277</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119548688</v>
+        <v>119548682</v>
       </c>
       <c r="B100" t="n">
         <v>79144</v>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480578</v>
+        <v>480635</v>
       </c>
       <c r="R100" t="n">
-        <v>6826046</v>
+        <v>6826107</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119548679</v>
+        <v>119548688</v>
       </c>
       <c r="B101" t="n">
         <v>79144</v>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480541</v>
+        <v>480578</v>
       </c>
       <c r="R101" t="n">
-        <v>6826087</v>
+        <v>6826046</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119548687</v>
+        <v>119548679</v>
       </c>
       <c r="B102" t="n">
         <v>79144</v>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>480571</v>
+        <v>480541</v>
       </c>
       <c r="R102" t="n">
-        <v>6826019</v>
+        <v>6826087</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119548706</v>
+        <v>119548687</v>
       </c>
       <c r="B103" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11202,21 +11202,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480635</v>
+        <v>480571</v>
       </c>
       <c r="R103" t="n">
-        <v>6826136</v>
+        <v>6826019</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119548681</v>
+        <v>119548980</v>
       </c>
       <c r="B104" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11300,38 +11300,47 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480634</v>
+        <v>480624</v>
       </c>
       <c r="R104" t="n">
-        <v>6826136</v>
+        <v>6826016</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11390,10 +11399,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119548684</v>
+        <v>119548745</v>
       </c>
       <c r="B105" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11406,21 +11415,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11430,10 +11439,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480648</v>
+        <v>480226</v>
       </c>
       <c r="R105" t="n">
-        <v>6826037</v>
+        <v>6826322</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11492,10 +11501,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119548980</v>
+        <v>119548769</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11504,47 +11513,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480624</v>
+        <v>480226</v>
       </c>
       <c r="R106" t="n">
-        <v>6826016</v>
+        <v>6826321</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11603,10 +11603,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548745</v>
+        <v>119548937</v>
       </c>
       <c r="B107" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11615,38 +11615,47 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480226</v>
+        <v>480612</v>
       </c>
       <c r="R107" t="n">
-        <v>6826322</v>
+        <v>6826127</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11705,10 +11714,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548769</v>
+        <v>119548681</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11721,21 +11730,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11745,10 +11754,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480226</v>
+        <v>480634</v>
       </c>
       <c r="R108" t="n">
-        <v>6826321</v>
+        <v>6826136</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11807,10 +11816,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548937</v>
+        <v>119548684</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11819,47 +11828,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480612</v>
+        <v>480648</v>
       </c>
       <c r="R109" t="n">
-        <v>6826127</v>
+        <v>6826037</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12836,10 +12836,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119549035</v>
+        <v>119548587</v>
       </c>
       <c r="B119" t="n">
-        <v>91832</v>
+        <v>91836</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12848,25 +12848,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4361</v>
+        <v>4363</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>480275</v>
+        <v>480252</v>
       </c>
       <c r="R119" t="n">
-        <v>6826360</v>
+        <v>6826381</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119548761</v>
+        <v>119548680</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12954,21 +12954,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>480311</v>
+        <v>480609</v>
       </c>
       <c r="R120" t="n">
-        <v>6826268</v>
+        <v>6826134</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119548768</v>
+        <v>119549035</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13056,21 +13056,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13080,10 +13080,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480257</v>
+        <v>480275</v>
       </c>
       <c r="R121" t="n">
-        <v>6826287</v>
+        <v>6826360</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13142,10 +13142,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119548680</v>
+        <v>119548761</v>
       </c>
       <c r="B122" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13158,21 +13158,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13182,10 +13182,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480609</v>
+        <v>480311</v>
       </c>
       <c r="R122" t="n">
-        <v>6826134</v>
+        <v>6826268</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13244,10 +13244,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119548587</v>
+        <v>119548768</v>
       </c>
       <c r="B123" t="n">
-        <v>91836</v>
+        <v>78526</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13256,25 +13256,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4363</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480252</v>
+        <v>480257</v>
       </c>
       <c r="R123" t="n">
-        <v>6826381</v>
+        <v>6826287</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119548976</v>
+        <v>119549023</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13358,47 +13358,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480358</v>
+        <v>480611</v>
       </c>
       <c r="R124" t="n">
-        <v>6826256</v>
+        <v>6826011</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13457,10 +13448,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119548770</v>
+        <v>119549022</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13473,21 +13464,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13497,10 +13488,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480222</v>
+        <v>480612</v>
       </c>
       <c r="R125" t="n">
-        <v>6826323</v>
+        <v>6826012</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13559,10 +13550,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548743</v>
+        <v>119548924</v>
       </c>
       <c r="B126" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13575,21 +13566,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13599,10 +13590,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480578</v>
+        <v>480630</v>
       </c>
       <c r="R126" t="n">
-        <v>6826046</v>
+        <v>6826048</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13661,10 +13652,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119548924</v>
+        <v>119548976</v>
       </c>
       <c r="B127" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13673,38 +13664,47 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480630</v>
+        <v>480358</v>
       </c>
       <c r="R127" t="n">
-        <v>6826048</v>
+        <v>6826256</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13763,10 +13763,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548696</v>
+        <v>119548770</v>
       </c>
       <c r="B128" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13779,21 +13779,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480493</v>
+        <v>480222</v>
       </c>
       <c r="R128" t="n">
-        <v>6826131</v>
+        <v>6826323</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13865,10 +13865,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548737</v>
+        <v>119548743</v>
       </c>
       <c r="B129" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13881,21 +13881,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13905,10 +13905,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480500</v>
+        <v>480578</v>
       </c>
       <c r="R129" t="n">
-        <v>6826127</v>
+        <v>6826046</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13967,10 +13967,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119549023</v>
+        <v>119548691</v>
       </c>
       <c r="B130" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13983,21 +13983,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14007,10 +14007,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480611</v>
+        <v>480539</v>
       </c>
       <c r="R130" t="n">
-        <v>6826011</v>
+        <v>6826061</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14069,10 +14069,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119549022</v>
+        <v>119548696</v>
       </c>
       <c r="B131" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14085,21 +14085,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14109,10 +14109,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480612</v>
+        <v>480493</v>
       </c>
       <c r="R131" t="n">
-        <v>6826012</v>
+        <v>6826131</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14171,10 +14171,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548691</v>
+        <v>119548737</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14187,21 +14187,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14211,10 +14211,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480539</v>
+        <v>480500</v>
       </c>
       <c r="R132" t="n">
-        <v>6826061</v>
+        <v>6826127</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14273,10 +14273,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548922</v>
+        <v>119549027</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14289,21 +14289,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480630</v>
+        <v>480581</v>
       </c>
       <c r="R133" t="n">
-        <v>6826050</v>
+        <v>6826018</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548689</v>
+        <v>119548922</v>
       </c>
       <c r="B134" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14415,10 +14415,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480563</v>
+        <v>480630</v>
       </c>
       <c r="R134" t="n">
-        <v>6826040</v>
+        <v>6826050</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14477,10 +14477,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119549027</v>
+        <v>119548689</v>
       </c>
       <c r="B135" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14493,21 +14493,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480581</v>
+        <v>480563</v>
       </c>
       <c r="R135" t="n">
-        <v>6826018</v>
+        <v>6826040</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -4058,10 +4058,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119548979</v>
+        <v>119548678</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,47 +4070,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480603</v>
+        <v>480510</v>
       </c>
       <c r="R34" t="n">
-        <v>6826118</v>
+        <v>6826101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,10 +4160,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119548948</v>
+        <v>119548686</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4181,47 +4172,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480229</v>
+        <v>480581</v>
       </c>
       <c r="R35" t="n">
-        <v>6826382</v>
+        <v>6826014</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4280,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119548763</v>
+        <v>119548595</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4296,21 +4278,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4320,10 +4302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480302</v>
+        <v>480235</v>
       </c>
       <c r="R36" t="n">
-        <v>6826281</v>
+        <v>6826296</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4382,10 +4364,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119548678</v>
+        <v>119548979</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4394,38 +4376,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480510</v>
+        <v>480603</v>
       </c>
       <c r="R37" t="n">
-        <v>6826101</v>
+        <v>6826118</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4484,10 +4475,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119548686</v>
+        <v>119548948</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4496,38 +4487,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480581</v>
+        <v>480229</v>
       </c>
       <c r="R38" t="n">
-        <v>6826014</v>
+        <v>6826382</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119548595</v>
+        <v>119548763</v>
       </c>
       <c r="B39" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480235</v>
+        <v>480302</v>
       </c>
       <c r="R39" t="n">
-        <v>6826296</v>
+        <v>6826281</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -9332,10 +9332,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119548598</v>
+        <v>119548925</v>
       </c>
       <c r="B85" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9348,21 +9348,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9372,10 +9372,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480260</v>
+        <v>480632</v>
       </c>
       <c r="R85" t="n">
-        <v>6826367</v>
+        <v>6826030</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9434,7 +9434,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119548925</v>
+        <v>119548911</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480632</v>
+        <v>480588</v>
       </c>
       <c r="R86" t="n">
-        <v>6826030</v>
+        <v>6826137</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119548911</v>
+        <v>119548741</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9552,21 +9552,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480588</v>
+        <v>480229</v>
       </c>
       <c r="R87" t="n">
-        <v>6826137</v>
+        <v>6826288</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119548741</v>
+        <v>119548598</v>
       </c>
       <c r="B88" t="n">
-        <v>79607</v>
+        <v>78560</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9654,21 +9654,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480229</v>
+        <v>480260</v>
       </c>
       <c r="R88" t="n">
-        <v>6826288</v>
+        <v>6826367</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119548706</v>
+        <v>119549030</v>
       </c>
       <c r="B89" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9756,21 +9756,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9780,10 +9780,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480635</v>
+        <v>480568</v>
       </c>
       <c r="R89" t="n">
-        <v>6826136</v>
+        <v>6826020</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119549030</v>
+        <v>119549025</v>
       </c>
       <c r="B90" t="n">
         <v>78171</v>
@@ -9882,10 +9882,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480568</v>
+        <v>480604</v>
       </c>
       <c r="R90" t="n">
-        <v>6826020</v>
+        <v>6826016</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9944,10 +9944,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119549025</v>
+        <v>119548648</v>
       </c>
       <c r="B91" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480604</v>
+        <v>480609</v>
       </c>
       <c r="R91" t="n">
-        <v>6826016</v>
+        <v>6826065</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548648</v>
+        <v>119548594</v>
       </c>
       <c r="B92" t="n">
         <v>78560</v>
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480609</v>
+        <v>480261</v>
       </c>
       <c r="R92" t="n">
-        <v>6826065</v>
+        <v>6826289</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10148,10 +10148,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119548594</v>
+        <v>119549026</v>
       </c>
       <c r="B93" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10164,21 +10164,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10188,10 +10188,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480261</v>
+        <v>480579</v>
       </c>
       <c r="R93" t="n">
-        <v>6826289</v>
+        <v>6826019</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119549026</v>
+        <v>119548974</v>
       </c>
       <c r="B94" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10262,38 +10262,47 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480579</v>
+        <v>480211</v>
       </c>
       <c r="R94" t="n">
-        <v>6826019</v>
+        <v>6826353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10352,10 +10361,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119548974</v>
+        <v>119548722</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10368,26 +10377,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10401,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480211</v>
+        <v>480236</v>
       </c>
       <c r="R95" t="n">
-        <v>6826353</v>
+        <v>6826375</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10463,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119548722</v>
+        <v>119548767</v>
       </c>
       <c r="B96" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10475,47 +10484,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480236</v>
+        <v>480266</v>
       </c>
       <c r="R96" t="n">
-        <v>6826375</v>
+        <v>6826294</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119548767</v>
+        <v>119548776</v>
       </c>
       <c r="B97" t="n">
         <v>78526</v>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480266</v>
+        <v>480250</v>
       </c>
       <c r="R97" t="n">
-        <v>6826294</v>
+        <v>6826379</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119548776</v>
+        <v>119548762</v>
       </c>
       <c r="B98" t="n">
         <v>78526</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480250</v>
+        <v>480309</v>
       </c>
       <c r="R98" t="n">
-        <v>6826379</v>
+        <v>6826277</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119548762</v>
+        <v>119548682</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10794,21 +10794,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480309</v>
+        <v>480635</v>
       </c>
       <c r="R99" t="n">
-        <v>6826277</v>
+        <v>6826107</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119548682</v>
+        <v>119548688</v>
       </c>
       <c r="B100" t="n">
         <v>79144</v>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480635</v>
+        <v>480578</v>
       </c>
       <c r="R100" t="n">
-        <v>6826107</v>
+        <v>6826046</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119548688</v>
+        <v>119548679</v>
       </c>
       <c r="B101" t="n">
         <v>79144</v>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480578</v>
+        <v>480541</v>
       </c>
       <c r="R101" t="n">
-        <v>6826046</v>
+        <v>6826087</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119548679</v>
+        <v>119548687</v>
       </c>
       <c r="B102" t="n">
         <v>79144</v>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>480541</v>
+        <v>480571</v>
       </c>
       <c r="R102" t="n">
-        <v>6826087</v>
+        <v>6826019</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119548687</v>
+        <v>119548706</v>
       </c>
       <c r="B103" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11202,21 +11202,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480571</v>
+        <v>480635</v>
       </c>
       <c r="R103" t="n">
-        <v>6826019</v>
+        <v>6826136</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119548980</v>
+        <v>119548681</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11300,47 +11300,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480624</v>
+        <v>480634</v>
       </c>
       <c r="R104" t="n">
-        <v>6826016</v>
+        <v>6826136</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11399,10 +11390,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119548745</v>
+        <v>119548684</v>
       </c>
       <c r="B105" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,21 +11406,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11439,10 +11430,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480226</v>
+        <v>480648</v>
       </c>
       <c r="R105" t="n">
-        <v>6826322</v>
+        <v>6826037</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11501,10 +11492,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119548769</v>
+        <v>119548980</v>
       </c>
       <c r="B106" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11513,38 +11504,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480226</v>
+        <v>480624</v>
       </c>
       <c r="R106" t="n">
-        <v>6826321</v>
+        <v>6826016</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11603,10 +11603,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548937</v>
+        <v>119548745</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11615,47 +11615,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480612</v>
+        <v>480226</v>
       </c>
       <c r="R107" t="n">
-        <v>6826127</v>
+        <v>6826322</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11714,10 +11705,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548681</v>
+        <v>119548769</v>
       </c>
       <c r="B108" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11730,21 +11721,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11754,10 +11745,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480634</v>
+        <v>480226</v>
       </c>
       <c r="R108" t="n">
-        <v>6826136</v>
+        <v>6826321</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11816,10 +11807,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548684</v>
+        <v>119548937</v>
       </c>
       <c r="B109" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11828,38 +11819,47 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480648</v>
+        <v>480612</v>
       </c>
       <c r="R109" t="n">
-        <v>6826037</v>
+        <v>6826127</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119549023</v>
+        <v>119548976</v>
       </c>
       <c r="B124" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13358,38 +13358,47 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480611</v>
+        <v>480358</v>
       </c>
       <c r="R124" t="n">
-        <v>6826011</v>
+        <v>6826256</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13448,10 +13457,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119549022</v>
+        <v>119548770</v>
       </c>
       <c r="B125" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13464,21 +13473,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13488,10 +13497,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480612</v>
+        <v>480222</v>
       </c>
       <c r="R125" t="n">
-        <v>6826012</v>
+        <v>6826323</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13550,10 +13559,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548924</v>
+        <v>119548743</v>
       </c>
       <c r="B126" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13566,21 +13575,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13590,10 +13599,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480630</v>
+        <v>480578</v>
       </c>
       <c r="R126" t="n">
-        <v>6826048</v>
+        <v>6826046</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13652,10 +13661,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119548976</v>
+        <v>119548924</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13664,47 +13673,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480358</v>
+        <v>480630</v>
       </c>
       <c r="R127" t="n">
-        <v>6826256</v>
+        <v>6826048</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13763,10 +13763,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548770</v>
+        <v>119548696</v>
       </c>
       <c r="B128" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13779,21 +13779,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480222</v>
+        <v>480493</v>
       </c>
       <c r="R128" t="n">
-        <v>6826323</v>
+        <v>6826131</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13865,10 +13865,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548743</v>
+        <v>119548737</v>
       </c>
       <c r="B129" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13881,21 +13881,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13905,10 +13905,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480578</v>
+        <v>480500</v>
       </c>
       <c r="R129" t="n">
-        <v>6826046</v>
+        <v>6826127</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13967,10 +13967,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119548691</v>
+        <v>119549023</v>
       </c>
       <c r="B130" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13983,21 +13983,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14007,10 +14007,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480539</v>
+        <v>480611</v>
       </c>
       <c r="R130" t="n">
-        <v>6826061</v>
+        <v>6826011</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14069,10 +14069,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119548696</v>
+        <v>119549022</v>
       </c>
       <c r="B131" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14085,21 +14085,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14109,10 +14109,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480493</v>
+        <v>480612</v>
       </c>
       <c r="R131" t="n">
-        <v>6826131</v>
+        <v>6826012</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14171,10 +14171,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548737</v>
+        <v>119548691</v>
       </c>
       <c r="B132" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14187,21 +14187,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14211,10 +14211,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480500</v>
+        <v>480539</v>
       </c>
       <c r="R132" t="n">
-        <v>6826127</v>
+        <v>6826061</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14273,10 +14273,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119549027</v>
+        <v>119548922</v>
       </c>
       <c r="B133" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14289,21 +14289,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480581</v>
+        <v>480630</v>
       </c>
       <c r="R133" t="n">
-        <v>6826018</v>
+        <v>6826050</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548922</v>
+        <v>119548689</v>
       </c>
       <c r="B134" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14415,10 +14415,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480630</v>
+        <v>480563</v>
       </c>
       <c r="R134" t="n">
-        <v>6826050</v>
+        <v>6826040</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14477,10 +14477,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119548689</v>
+        <v>119549027</v>
       </c>
       <c r="B135" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14493,21 +14493,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480563</v>
+        <v>480581</v>
       </c>
       <c r="R135" t="n">
-        <v>6826040</v>
+        <v>6826018</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14579,10 +14579,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119548751</v>
+        <v>119548916</v>
       </c>
       <c r="B136" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14595,21 +14595,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14619,10 +14619,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480657</v>
+        <v>480586</v>
       </c>
       <c r="R136" t="n">
-        <v>6826036</v>
+        <v>6826085</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14681,10 +14681,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119548777</v>
+        <v>119548973</v>
       </c>
       <c r="B137" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14693,25 +14693,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480260</v>
+        <v>480617</v>
       </c>
       <c r="R137" t="n">
-        <v>6826367</v>
+        <v>6826130</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14783,10 +14783,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119548916</v>
+        <v>119548675</v>
       </c>
       <c r="B138" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14799,21 +14799,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14823,10 +14823,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480586</v>
+        <v>480451</v>
       </c>
       <c r="R138" t="n">
-        <v>6826085</v>
+        <v>6826172</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14885,10 +14885,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119548973</v>
+        <v>119548637</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14897,25 +14897,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480617</v>
+        <v>480555</v>
       </c>
       <c r="R139" t="n">
-        <v>6826130</v>
+        <v>6826106</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14987,10 +14987,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119548675</v>
+        <v>119548640</v>
       </c>
       <c r="B140" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15003,21 +15003,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15027,10 +15027,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480451</v>
+        <v>480602</v>
       </c>
       <c r="R140" t="n">
-        <v>6826172</v>
+        <v>6826132</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119548637</v>
+        <v>119549021</v>
       </c>
       <c r="B141" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15105,21 +15105,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480555</v>
+        <v>480634</v>
       </c>
       <c r="R141" t="n">
-        <v>6826106</v>
+        <v>6826019</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15191,10 +15191,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119548640</v>
+        <v>119548729</v>
       </c>
       <c r="B142" t="n">
-        <v>78560</v>
+        <v>91852</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15203,25 +15203,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>4366</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>480602</v>
+        <v>480546</v>
       </c>
       <c r="R142" t="n">
-        <v>6826132</v>
+        <v>6826055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15293,10 +15293,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119549021</v>
+        <v>119548751</v>
       </c>
       <c r="B143" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15309,21 +15309,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15333,10 +15333,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>480634</v>
+        <v>480657</v>
       </c>
       <c r="R143" t="n">
-        <v>6826019</v>
+        <v>6826036</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15395,10 +15395,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119548729</v>
+        <v>119548777</v>
       </c>
       <c r="B144" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15407,25 +15407,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>480546</v>
+        <v>480260</v>
       </c>
       <c r="R144" t="n">
-        <v>6826055</v>
+        <v>6826367</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -3344,7 +3344,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119549032</v>
+        <v>119549016</v>
       </c>
       <c r="B27" t="n">
         <v>78171</v>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480575</v>
+        <v>480508</v>
       </c>
       <c r="R27" t="n">
-        <v>6826022</v>
+        <v>6826102</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119549038</v>
+        <v>119548948</v>
       </c>
       <c r="B28" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,38 +3458,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480584</v>
+        <v>480229</v>
       </c>
       <c r="R28" t="n">
-        <v>6826087</v>
+        <v>6826382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,10 +3557,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119548779</v>
+        <v>119548983</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,25 +3569,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3588,10 +3597,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480282</v>
+        <v>480586</v>
       </c>
       <c r="R29" t="n">
-        <v>6826360</v>
+        <v>6826020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,10 +3659,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119548744</v>
+        <v>119548915</v>
       </c>
       <c r="B30" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3666,21 +3675,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3690,10 +3699,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480408</v>
+        <v>480639</v>
       </c>
       <c r="R30" t="n">
-        <v>6826259</v>
+        <v>6826111</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,10 +3761,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119548728</v>
+        <v>119548765</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,25 +3773,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3792,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480559</v>
+        <v>480273</v>
       </c>
       <c r="R31" t="n">
-        <v>6826033</v>
+        <v>6826297</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,10 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119548740</v>
+        <v>119548590</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>78560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3870,21 +3879,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,7 +3906,7 @@
         <v>480405</v>
       </c>
       <c r="R32" t="n">
-        <v>6826234</v>
+        <v>6826236</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119548650</v>
+        <v>119548986</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3972,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3996,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480226</v>
+        <v>480423</v>
       </c>
       <c r="R33" t="n">
-        <v>6826322</v>
+        <v>6826303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119548678</v>
+        <v>119548932</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,38 +4079,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480510</v>
+        <v>480205</v>
       </c>
       <c r="R34" t="n">
-        <v>6826101</v>
+        <v>6826355</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,10 +4178,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119548686</v>
+        <v>119548724</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,38 +4190,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480581</v>
+        <v>480417</v>
       </c>
       <c r="R35" t="n">
-        <v>6826014</v>
+        <v>6826298</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,7 +4289,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119548595</v>
+        <v>119548642</v>
       </c>
       <c r="B36" t="n">
         <v>78560</v>
@@ -4302,10 +4329,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480235</v>
+        <v>480660</v>
       </c>
       <c r="R36" t="n">
-        <v>6826296</v>
+        <v>6826105</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,10 +4391,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119548979</v>
+        <v>119548763</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4376,47 +4403,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480603</v>
+        <v>480302</v>
       </c>
       <c r="R37" t="n">
-        <v>6826118</v>
+        <v>6826281</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119548948</v>
+        <v>119548689</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4487,47 +4505,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480229</v>
+        <v>480563</v>
       </c>
       <c r="R38" t="n">
-        <v>6826382</v>
+        <v>6826040</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4586,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119548763</v>
+        <v>119548684</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4602,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4626,10 +4635,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480302</v>
+        <v>480648</v>
       </c>
       <c r="R39" t="n">
-        <v>6826281</v>
+        <v>6826037</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4688,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119548593</v>
+        <v>119548740</v>
       </c>
       <c r="B40" t="n">
-        <v>78560</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4704,21 +4713,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4728,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480302</v>
+        <v>480405</v>
       </c>
       <c r="R40" t="n">
-        <v>6826281</v>
+        <v>6826234</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119548983</v>
+        <v>119549022</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4802,25 +4811,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4830,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480586</v>
+        <v>480612</v>
       </c>
       <c r="R41" t="n">
-        <v>6826020</v>
+        <v>6826012</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,7 +4901,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119548921</v>
+        <v>119548777</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4932,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480627</v>
+        <v>480260</v>
       </c>
       <c r="R42" t="n">
-        <v>6826045</v>
+        <v>6826367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119548910</v>
+        <v>119548921</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5034,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480590</v>
+        <v>480627</v>
       </c>
       <c r="R43" t="n">
-        <v>6826131</v>
+        <v>6826045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119548764</v>
+        <v>119548648</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5112,21 +5121,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5136,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480294</v>
+        <v>480609</v>
       </c>
       <c r="R44" t="n">
-        <v>6826287</v>
+        <v>6826065</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,10 +5207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119548723</v>
+        <v>119548599</v>
       </c>
       <c r="B45" t="n">
-        <v>91852</v>
+        <v>78560</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5210,47 +5219,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480609</v>
+        <v>480302</v>
       </c>
       <c r="R45" t="n">
-        <v>6826134</v>
+        <v>6826343</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119548711</v>
+        <v>119549020</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5325,43 +5325,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480252</v>
+        <v>480645</v>
       </c>
       <c r="R46" t="n">
-        <v>6826381</v>
+        <v>6826039</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5420,7 +5411,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119548986</v>
+        <v>119549018</v>
       </c>
       <c r="B47" t="n">
         <v>78171</v>
@@ -5460,10 +5451,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480423</v>
+        <v>480657</v>
       </c>
       <c r="R47" t="n">
-        <v>6826303</v>
+        <v>6826051</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5522,10 +5513,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119548985</v>
+        <v>119548910</v>
       </c>
       <c r="B48" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5538,21 +5529,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5562,10 +5553,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480393</v>
+        <v>480590</v>
       </c>
       <c r="R48" t="n">
-        <v>6826311</v>
+        <v>6826131</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5624,7 +5615,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119548778</v>
+        <v>119548771</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -5664,10 +5655,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480271</v>
+        <v>480219</v>
       </c>
       <c r="R49" t="n">
-        <v>6826362</v>
+        <v>6826332</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5726,10 +5717,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119548909</v>
+        <v>119548980</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5738,38 +5729,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480580</v>
+        <v>480624</v>
       </c>
       <c r="R50" t="n">
-        <v>6826101</v>
+        <v>6826016</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119548591</v>
+        <v>119548737</v>
       </c>
       <c r="B51" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,21 +5844,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480351</v>
+        <v>480500</v>
       </c>
       <c r="R51" t="n">
-        <v>6826254</v>
+        <v>6826127</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119548642</v>
+        <v>119548638</v>
       </c>
       <c r="B52" t="n">
         <v>78560</v>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480660</v>
+        <v>480579</v>
       </c>
       <c r="R52" t="n">
-        <v>6826105</v>
+        <v>6826099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119548771</v>
+        <v>119548597</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480219</v>
+        <v>480202</v>
       </c>
       <c r="R53" t="n">
-        <v>6826332</v>
+        <v>6826368</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119548752</v>
+        <v>119549034</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6150,21 +6150,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480634</v>
+        <v>480553</v>
       </c>
       <c r="R54" t="n">
-        <v>6826136</v>
+        <v>6826047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119548714</v>
+        <v>119549030</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480294</v>
+        <v>480568</v>
       </c>
       <c r="R55" t="n">
-        <v>6826358</v>
+        <v>6826020</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119548739</v>
+        <v>119548691</v>
       </c>
       <c r="B56" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480598</v>
+        <v>480539</v>
       </c>
       <c r="R56" t="n">
-        <v>6826021</v>
+        <v>6826061</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119549019</v>
+        <v>119548931</v>
       </c>
       <c r="B57" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6452,38 +6452,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480650</v>
+        <v>480222</v>
       </c>
       <c r="R57" t="n">
-        <v>6826031</v>
+        <v>6826323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6542,10 +6551,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119548690</v>
+        <v>119548759</v>
       </c>
       <c r="B58" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6558,21 +6567,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6582,10 +6591,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480543</v>
+        <v>480354</v>
       </c>
       <c r="R58" t="n">
-        <v>6826055</v>
+        <v>6826256</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6644,10 +6653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119548932</v>
+        <v>119548688</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6656,47 +6665,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480205</v>
+        <v>480578</v>
       </c>
       <c r="R59" t="n">
-        <v>6826355</v>
+        <v>6826046</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,10 +6755,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119548774</v>
+        <v>119548686</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480232</v>
+        <v>480581</v>
       </c>
       <c r="R60" t="n">
-        <v>6826378</v>
+        <v>6826014</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,10 +6857,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119548912</v>
+        <v>119548982</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6869,38 +6869,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480641</v>
+        <v>480584</v>
       </c>
       <c r="R61" t="n">
-        <v>6826128</v>
+        <v>6826037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6959,10 +6968,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548749</v>
+        <v>119548979</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6971,38 +6980,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480500</v>
+        <v>480603</v>
       </c>
       <c r="R62" t="n">
-        <v>6826126</v>
+        <v>6826118</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7061,10 +7079,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548758</v>
+        <v>119548714</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7077,21 +7095,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7101,10 +7119,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480401</v>
+        <v>480294</v>
       </c>
       <c r="R63" t="n">
-        <v>6826229</v>
+        <v>6826358</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7163,10 +7181,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548641</v>
+        <v>119548776</v>
       </c>
       <c r="B64" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7179,21 +7197,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7203,10 +7221,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480602</v>
+        <v>480250</v>
       </c>
       <c r="R64" t="n">
-        <v>6826129</v>
+        <v>6826379</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7265,10 +7283,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548649</v>
+        <v>119548760</v>
       </c>
       <c r="B65" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7281,21 +7299,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7305,10 +7323,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480632</v>
+        <v>480323</v>
       </c>
       <c r="R65" t="n">
-        <v>6826029</v>
+        <v>6826258</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7367,10 +7385,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119548636</v>
+        <v>119548744</v>
       </c>
       <c r="B66" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7383,21 +7401,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7407,10 +7425,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480537</v>
+        <v>480408</v>
       </c>
       <c r="R66" t="n">
-        <v>6826085</v>
+        <v>6826259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7469,10 +7487,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119549031</v>
+        <v>119548687</v>
       </c>
       <c r="B67" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7485,21 +7503,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7509,7 +7527,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480572</v>
+        <v>480571</v>
       </c>
       <c r="R67" t="n">
         <v>6826019</v>
@@ -7571,10 +7589,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119548589</v>
+        <v>119549024</v>
       </c>
       <c r="B68" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7587,21 +7605,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7611,10 +7629,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480414</v>
+        <v>480607</v>
       </c>
       <c r="R68" t="n">
-        <v>6826211</v>
+        <v>6826012</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7673,10 +7691,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119548928</v>
+        <v>119548770</v>
       </c>
       <c r="B69" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7707,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7731,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480563</v>
+        <v>480222</v>
       </c>
       <c r="R69" t="n">
-        <v>6826040</v>
+        <v>6826323</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7775,10 +7793,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119548982</v>
+        <v>119548913</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7787,47 +7805,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480584</v>
+        <v>480660</v>
       </c>
       <c r="R70" t="n">
-        <v>6826037</v>
+        <v>6826105</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7886,10 +7895,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119548981</v>
+        <v>119548772</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7898,47 +7907,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480644</v>
+        <v>480202</v>
       </c>
       <c r="R71" t="n">
-        <v>6826039</v>
+        <v>6826368</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7997,7 +7997,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119548651</v>
+        <v>119548682</v>
       </c>
       <c r="B72" t="n">
         <v>79144</v>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480424</v>
+        <v>480635</v>
       </c>
       <c r="R72" t="n">
-        <v>6826300</v>
+        <v>6826107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119548676</v>
+        <v>119548937</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8111,38 +8111,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480460</v>
+        <v>480612</v>
       </c>
       <c r="R73" t="n">
-        <v>6826167</v>
+        <v>6826127</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8201,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119548913</v>
+        <v>119548959</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8213,38 +8222,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480660</v>
+        <v>480651</v>
       </c>
       <c r="R74" t="n">
-        <v>6826105</v>
+        <v>6826110</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8303,10 +8321,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119548677</v>
+        <v>119548596</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8319,21 +8337,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8343,10 +8361,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480500</v>
+        <v>480220</v>
       </c>
       <c r="R75" t="n">
-        <v>6826126</v>
+        <v>6826344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8405,10 +8423,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119548730</v>
+        <v>119548598</v>
       </c>
       <c r="B76" t="n">
-        <v>91856</v>
+        <v>78560</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8421,21 +8439,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8445,10 +8463,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480608</v>
+        <v>480260</v>
       </c>
       <c r="R76" t="n">
-        <v>6826130</v>
+        <v>6826367</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8507,10 +8525,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119548590</v>
+        <v>119548764</v>
       </c>
       <c r="B77" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8523,21 +8541,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8547,10 +8565,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480405</v>
+        <v>480294</v>
       </c>
       <c r="R77" t="n">
-        <v>6826236</v>
+        <v>6826287</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8609,10 +8627,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119548599</v>
+        <v>119548651</v>
       </c>
       <c r="B78" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8625,21 +8643,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8649,10 +8667,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480302</v>
+        <v>480424</v>
       </c>
       <c r="R78" t="n">
-        <v>6826343</v>
+        <v>6826300</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8711,10 +8729,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119548772</v>
+        <v>119549026</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8727,21 +8745,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8751,10 +8769,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480202</v>
+        <v>480579</v>
       </c>
       <c r="R79" t="n">
-        <v>6826368</v>
+        <v>6826019</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8813,10 +8831,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548959</v>
+        <v>119548639</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8825,47 +8843,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480651</v>
+        <v>480587</v>
       </c>
       <c r="R80" t="n">
-        <v>6826110</v>
+        <v>6826137</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8924,10 +8933,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119549034</v>
+        <v>119548649</v>
       </c>
       <c r="B81" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8940,21 +8949,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8964,10 +8973,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480553</v>
+        <v>480632</v>
       </c>
       <c r="R81" t="n">
-        <v>6826047</v>
+        <v>6826029</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9026,10 +9035,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119548697</v>
+        <v>119549035</v>
       </c>
       <c r="B82" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9042,21 +9051,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9066,10 +9075,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480557</v>
+        <v>480275</v>
       </c>
       <c r="R82" t="n">
-        <v>6826036</v>
+        <v>6826360</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9128,10 +9137,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119548760</v>
+        <v>119549033</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9144,21 +9153,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9168,10 +9177,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480323</v>
+        <v>480552</v>
       </c>
       <c r="R83" t="n">
-        <v>6826258</v>
+        <v>6826035</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9230,10 +9239,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119548588</v>
+        <v>119549019</v>
       </c>
       <c r="B84" t="n">
-        <v>74638</v>
+        <v>78171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9246,21 +9255,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9270,10 +9279,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480240</v>
+        <v>480650</v>
       </c>
       <c r="R84" t="n">
-        <v>6826296</v>
+        <v>6826031</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9332,10 +9341,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119548925</v>
+        <v>119548711</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9348,34 +9357,43 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480632</v>
+        <v>480252</v>
       </c>
       <c r="R85" t="n">
-        <v>6826030</v>
+        <v>6826381</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9434,7 +9452,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119548911</v>
+        <v>119548914</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -9474,10 +9492,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480588</v>
+        <v>480642</v>
       </c>
       <c r="R86" t="n">
-        <v>6826137</v>
+        <v>6826105</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9536,10 +9554,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119548741</v>
+        <v>119549032</v>
       </c>
       <c r="B87" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9552,21 +9570,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9576,10 +9594,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480229</v>
+        <v>480575</v>
       </c>
       <c r="R87" t="n">
-        <v>6826288</v>
+        <v>6826022</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9638,10 +9656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119548598</v>
+        <v>119548739</v>
       </c>
       <c r="B88" t="n">
-        <v>78560</v>
+        <v>78263</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9654,21 +9672,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9678,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480260</v>
+        <v>480598</v>
       </c>
       <c r="R88" t="n">
-        <v>6826367</v>
+        <v>6826021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9740,10 +9758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119549030</v>
+        <v>119548595</v>
       </c>
       <c r="B89" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9756,21 +9774,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9780,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480568</v>
+        <v>480235</v>
       </c>
       <c r="R89" t="n">
-        <v>6826020</v>
+        <v>6826296</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,10 +9860,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119549025</v>
+        <v>119548922</v>
       </c>
       <c r="B90" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9858,21 +9876,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9882,10 +9900,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480604</v>
+        <v>480630</v>
       </c>
       <c r="R90" t="n">
-        <v>6826016</v>
+        <v>6826050</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9944,10 +9962,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119548648</v>
+        <v>119548761</v>
       </c>
       <c r="B91" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9960,21 +9978,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9984,10 +10002,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480609</v>
+        <v>480311</v>
       </c>
       <c r="R91" t="n">
-        <v>6826065</v>
+        <v>6826268</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10046,7 +10064,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548594</v>
+        <v>119548591</v>
       </c>
       <c r="B92" t="n">
         <v>78560</v>
@@ -10086,10 +10104,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480261</v>
+        <v>480351</v>
       </c>
       <c r="R92" t="n">
-        <v>6826289</v>
+        <v>6826254</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10148,10 +10166,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119549026</v>
+        <v>119548751</v>
       </c>
       <c r="B93" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10164,21 +10182,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10188,10 +10206,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480579</v>
+        <v>480657</v>
       </c>
       <c r="R93" t="n">
-        <v>6826019</v>
+        <v>6826036</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10250,10 +10268,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119548974</v>
+        <v>119549029</v>
       </c>
       <c r="B94" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10262,47 +10280,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480211</v>
+        <v>480565</v>
       </c>
       <c r="R94" t="n">
-        <v>6826353</v>
+        <v>6826017</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10361,10 +10370,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119548722</v>
+        <v>119548758</v>
       </c>
       <c r="B95" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10373,47 +10382,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480236</v>
+        <v>480401</v>
       </c>
       <c r="R95" t="n">
-        <v>6826375</v>
+        <v>6826229</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119548767</v>
+        <v>119548768</v>
       </c>
       <c r="B96" t="n">
         <v>78526</v>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480266</v>
+        <v>480257</v>
       </c>
       <c r="R96" t="n">
-        <v>6826294</v>
+        <v>6826287</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119548776</v>
+        <v>119549031</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480250</v>
+        <v>480572</v>
       </c>
       <c r="R97" t="n">
-        <v>6826379</v>
+        <v>6826019</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,10 +10676,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119548762</v>
+        <v>119548681</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10692,21 +10692,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480309</v>
+        <v>480634</v>
       </c>
       <c r="R98" t="n">
-        <v>6826277</v>
+        <v>6826136</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119548682</v>
+        <v>119548679</v>
       </c>
       <c r="B99" t="n">
         <v>79144</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480635</v>
+        <v>480541</v>
       </c>
       <c r="R99" t="n">
-        <v>6826107</v>
+        <v>6826087</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,10 +10880,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119548688</v>
+        <v>119548718</v>
       </c>
       <c r="B100" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10896,21 +10896,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480578</v>
+        <v>480637</v>
       </c>
       <c r="R100" t="n">
-        <v>6826046</v>
+        <v>6826047</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10982,10 +10982,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119548679</v>
+        <v>119548697</v>
       </c>
       <c r="B101" t="n">
-        <v>79144</v>
+        <v>89633</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10998,21 +10998,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480541</v>
+        <v>480557</v>
       </c>
       <c r="R101" t="n">
-        <v>6826087</v>
+        <v>6826036</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11084,10 +11084,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119548687</v>
+        <v>119549021</v>
       </c>
       <c r="B102" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>480571</v>
+        <v>480634</v>
       </c>
       <c r="R102" t="n">
         <v>6826019</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119548706</v>
+        <v>119549025</v>
       </c>
       <c r="B103" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11202,21 +11202,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480635</v>
+        <v>480604</v>
       </c>
       <c r="R103" t="n">
-        <v>6826136</v>
+        <v>6826016</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119548681</v>
+        <v>119548745</v>
       </c>
       <c r="B104" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11304,21 +11304,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11328,10 +11328,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480634</v>
+        <v>480226</v>
       </c>
       <c r="R104" t="n">
-        <v>6826136</v>
+        <v>6826322</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11390,7 +11390,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119548684</v>
+        <v>119548675</v>
       </c>
       <c r="B105" t="n">
         <v>79144</v>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480648</v>
+        <v>480451</v>
       </c>
       <c r="R105" t="n">
-        <v>6826037</v>
+        <v>6826172</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119548980</v>
+        <v>119548973</v>
       </c>
       <c r="B106" t="n">
         <v>91840</v>
@@ -11525,26 +11525,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480624</v>
+        <v>480617</v>
       </c>
       <c r="R106" t="n">
-        <v>6826016</v>
+        <v>6826130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11603,10 +11594,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548745</v>
+        <v>119548779</v>
       </c>
       <c r="B107" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11619,21 +11610,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11643,10 +11634,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480226</v>
+        <v>480282</v>
       </c>
       <c r="R107" t="n">
-        <v>6826322</v>
+        <v>6826360</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11705,7 +11696,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548769</v>
+        <v>119548924</v>
       </c>
       <c r="B108" t="n">
         <v>78526</v>
@@ -11745,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480226</v>
+        <v>480630</v>
       </c>
       <c r="R108" t="n">
-        <v>6826321</v>
+        <v>6826048</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11807,10 +11798,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548937</v>
+        <v>119548912</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11819,47 +11810,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480612</v>
+        <v>480641</v>
       </c>
       <c r="R109" t="n">
-        <v>6826127</v>
+        <v>6826128</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11918,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119549016</v>
+        <v>119548723</v>
       </c>
       <c r="B110" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11930,38 +11912,47 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480508</v>
+        <v>480609</v>
       </c>
       <c r="R110" t="n">
-        <v>6826102</v>
+        <v>6826134</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12020,10 +12011,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119548596</v>
+        <v>119549027</v>
       </c>
       <c r="B111" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12036,21 +12027,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12060,10 +12051,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480220</v>
+        <v>480581</v>
       </c>
       <c r="R111" t="n">
-        <v>6826344</v>
+        <v>6826018</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12122,10 +12113,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119548765</v>
+        <v>119548637</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12138,21 +12129,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12162,10 +12153,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480273</v>
+        <v>480555</v>
       </c>
       <c r="R112" t="n">
-        <v>6826297</v>
+        <v>6826106</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12224,10 +12215,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119548759</v>
+        <v>119548589</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12240,21 +12231,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12264,10 +12255,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480354</v>
+        <v>480414</v>
       </c>
       <c r="R113" t="n">
-        <v>6826256</v>
+        <v>6826211</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12326,10 +12317,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119548915</v>
+        <v>119548587</v>
       </c>
       <c r="B114" t="n">
-        <v>78526</v>
+        <v>91836</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12338,25 +12329,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>4363</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12366,10 +12357,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480639</v>
+        <v>480252</v>
       </c>
       <c r="R114" t="n">
-        <v>6826111</v>
+        <v>6826381</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12428,7 +12419,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119548914</v>
+        <v>119548916</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12468,10 +12459,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480642</v>
+        <v>480586</v>
       </c>
       <c r="R115" t="n">
-        <v>6826105</v>
+        <v>6826085</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12530,10 +12521,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119548713</v>
+        <v>119548730</v>
       </c>
       <c r="B116" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12546,21 +12537,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12570,10 +12561,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>480232</v>
+        <v>480608</v>
       </c>
       <c r="R116" t="n">
-        <v>6826379</v>
+        <v>6826130</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12632,10 +12623,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119548718</v>
+        <v>119548762</v>
       </c>
       <c r="B117" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12648,21 +12639,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12672,10 +12663,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480637</v>
+        <v>480309</v>
       </c>
       <c r="R117" t="n">
-        <v>6826047</v>
+        <v>6826277</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12734,7 +12725,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119548635</v>
+        <v>119548640</v>
       </c>
       <c r="B118" t="n">
         <v>78560</v>
@@ -12774,10 +12765,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480439</v>
+        <v>480602</v>
       </c>
       <c r="R118" t="n">
-        <v>6826220</v>
+        <v>6826132</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12836,10 +12827,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119548587</v>
+        <v>119548594</v>
       </c>
       <c r="B119" t="n">
-        <v>91836</v>
+        <v>78560</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12848,25 +12839,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4363</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12876,10 +12867,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>480252</v>
+        <v>480261</v>
       </c>
       <c r="R119" t="n">
-        <v>6826381</v>
+        <v>6826289</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12938,10 +12929,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119548680</v>
+        <v>119548911</v>
       </c>
       <c r="B120" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12954,21 +12945,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12978,10 +12969,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>480609</v>
+        <v>480588</v>
       </c>
       <c r="R120" t="n">
-        <v>6826134</v>
+        <v>6826137</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13040,10 +13031,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119549035</v>
+        <v>119548925</v>
       </c>
       <c r="B121" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13056,21 +13047,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13080,10 +13071,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480275</v>
+        <v>480632</v>
       </c>
       <c r="R121" t="n">
-        <v>6826360</v>
+        <v>6826030</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13142,10 +13133,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119548761</v>
+        <v>119548743</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13158,21 +13149,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13182,10 +13173,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480311</v>
+        <v>480578</v>
       </c>
       <c r="R122" t="n">
-        <v>6826268</v>
+        <v>6826046</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13244,10 +13235,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119548768</v>
+        <v>119548696</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13260,21 +13251,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13284,10 +13275,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480257</v>
+        <v>480493</v>
       </c>
       <c r="R123" t="n">
-        <v>6826287</v>
+        <v>6826131</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13346,10 +13337,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119548976</v>
+        <v>119549038</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13358,47 +13349,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480358</v>
+        <v>480584</v>
       </c>
       <c r="R124" t="n">
-        <v>6826256</v>
+        <v>6826087</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13457,10 +13439,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119548770</v>
+        <v>119548752</v>
       </c>
       <c r="B125" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13473,21 +13455,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13497,10 +13479,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480222</v>
+        <v>480634</v>
       </c>
       <c r="R125" t="n">
-        <v>6826323</v>
+        <v>6826136</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13559,10 +13541,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548743</v>
+        <v>119548690</v>
       </c>
       <c r="B126" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13575,21 +13557,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13599,10 +13581,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480578</v>
+        <v>480543</v>
       </c>
       <c r="R126" t="n">
-        <v>6826046</v>
+        <v>6826055</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13661,10 +13643,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119548924</v>
+        <v>119548677</v>
       </c>
       <c r="B127" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13677,21 +13659,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13701,10 +13683,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480630</v>
+        <v>480500</v>
       </c>
       <c r="R127" t="n">
-        <v>6826048</v>
+        <v>6826126</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13763,10 +13745,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548696</v>
+        <v>119548728</v>
       </c>
       <c r="B128" t="n">
-        <v>79115</v>
+        <v>91852</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13775,25 +13757,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13803,10 +13785,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480493</v>
+        <v>480559</v>
       </c>
       <c r="R128" t="n">
-        <v>6826131</v>
+        <v>6826033</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13865,10 +13847,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548737</v>
+        <v>119548774</v>
       </c>
       <c r="B129" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13881,21 +13863,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13905,10 +13887,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480500</v>
+        <v>480232</v>
       </c>
       <c r="R129" t="n">
-        <v>6826127</v>
+        <v>6826378</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13967,10 +13949,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119549023</v>
+        <v>119548706</v>
       </c>
       <c r="B130" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13983,21 +13965,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14007,10 +13989,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480611</v>
+        <v>480635</v>
       </c>
       <c r="R130" t="n">
-        <v>6826011</v>
+        <v>6826136</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14069,7 +14051,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119549022</v>
+        <v>119548928</v>
       </c>
       <c r="B131" t="n">
         <v>78171</v>
@@ -14109,10 +14091,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480612</v>
+        <v>480563</v>
       </c>
       <c r="R131" t="n">
-        <v>6826012</v>
+        <v>6826040</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14171,10 +14153,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548691</v>
+        <v>119549023</v>
       </c>
       <c r="B132" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14187,21 +14169,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14211,10 +14193,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480539</v>
+        <v>480611</v>
       </c>
       <c r="R132" t="n">
-        <v>6826061</v>
+        <v>6826011</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14273,10 +14255,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548922</v>
+        <v>119548985</v>
       </c>
       <c r="B133" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14289,21 +14271,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14313,10 +14295,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480630</v>
+        <v>480393</v>
       </c>
       <c r="R133" t="n">
-        <v>6826050</v>
+        <v>6826311</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14375,10 +14357,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548689</v>
+        <v>119548713</v>
       </c>
       <c r="B134" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14391,21 +14373,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14415,10 +14397,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480563</v>
+        <v>480232</v>
       </c>
       <c r="R134" t="n">
-        <v>6826040</v>
+        <v>6826379</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14477,10 +14459,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119549027</v>
+        <v>119548909</v>
       </c>
       <c r="B135" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14493,21 +14475,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14517,10 +14499,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480581</v>
+        <v>480580</v>
       </c>
       <c r="R135" t="n">
-        <v>6826018</v>
+        <v>6826101</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14579,10 +14561,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119548916</v>
+        <v>119548685</v>
       </c>
       <c r="B136" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14595,21 +14577,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14619,10 +14601,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480586</v>
+        <v>480579</v>
       </c>
       <c r="R136" t="n">
-        <v>6826085</v>
+        <v>6826019</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14681,7 +14663,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119548973</v>
+        <v>119548974</v>
       </c>
       <c r="B137" t="n">
         <v>91840</v>
@@ -14714,17 +14696,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480617</v>
+        <v>480211</v>
       </c>
       <c r="R137" t="n">
-        <v>6826130</v>
+        <v>6826353</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14783,10 +14774,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119548675</v>
+        <v>119548729</v>
       </c>
       <c r="B138" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14795,25 +14786,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14823,10 +14814,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480451</v>
+        <v>480546</v>
       </c>
       <c r="R138" t="n">
-        <v>6826172</v>
+        <v>6826055</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14885,10 +14876,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119548637</v>
+        <v>119548722</v>
       </c>
       <c r="B139" t="n">
-        <v>78560</v>
+        <v>91852</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14897,38 +14888,47 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>4366</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480555</v>
+        <v>480236</v>
       </c>
       <c r="R139" t="n">
-        <v>6826106</v>
+        <v>6826375</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119548640</v>
+        <v>119548636</v>
       </c>
       <c r="B140" t="n">
         <v>78560</v>
@@ -15027,10 +15027,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480602</v>
+        <v>480537</v>
       </c>
       <c r="R140" t="n">
-        <v>6826132</v>
+        <v>6826085</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119549021</v>
+        <v>119548769</v>
       </c>
       <c r="B141" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15105,21 +15105,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480634</v>
+        <v>480226</v>
       </c>
       <c r="R141" t="n">
-        <v>6826019</v>
+        <v>6826321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15191,10 +15191,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119548729</v>
+        <v>119548767</v>
       </c>
       <c r="B142" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15203,25 +15203,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>480546</v>
+        <v>480266</v>
       </c>
       <c r="R142" t="n">
-        <v>6826055</v>
+        <v>6826294</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15293,10 +15293,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119548751</v>
+        <v>119548588</v>
       </c>
       <c r="B143" t="n">
-        <v>78262</v>
+        <v>74638</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15309,21 +15309,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15333,10 +15333,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>480657</v>
+        <v>480240</v>
       </c>
       <c r="R143" t="n">
-        <v>6826036</v>
+        <v>6826296</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15395,10 +15395,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119548777</v>
+        <v>119548650</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15411,21 +15411,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>480260</v>
+        <v>480226</v>
       </c>
       <c r="R144" t="n">
-        <v>6826367</v>
+        <v>6826322</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15497,7 +15497,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119548639</v>
+        <v>119548644</v>
       </c>
       <c r="B145" t="n">
         <v>78560</v>
@@ -15537,10 +15537,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480587</v>
+        <v>480584</v>
       </c>
       <c r="R145" t="n">
-        <v>6826137</v>
+        <v>6826096</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15599,7 +15599,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119548643</v>
+        <v>119548635</v>
       </c>
       <c r="B146" t="n">
         <v>78560</v>
@@ -15639,10 +15639,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480599</v>
+        <v>480439</v>
       </c>
       <c r="R146" t="n">
-        <v>6826114</v>
+        <v>6826220</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15701,10 +15701,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119549029</v>
+        <v>119548641</v>
       </c>
       <c r="B147" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15717,21 +15717,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15741,10 +15741,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480565</v>
+        <v>480602</v>
       </c>
       <c r="R147" t="n">
-        <v>6826017</v>
+        <v>6826129</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,10 +15803,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119549024</v>
+        <v>119548593</v>
       </c>
       <c r="B148" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15819,21 +15819,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480607</v>
+        <v>480302</v>
       </c>
       <c r="R148" t="n">
-        <v>6826012</v>
+        <v>6826281</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119548597</v>
+        <v>119548678</v>
       </c>
       <c r="B149" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15921,21 +15921,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15945,10 +15945,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480202</v>
+        <v>480510</v>
       </c>
       <c r="R149" t="n">
-        <v>6826368</v>
+        <v>6826101</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16007,10 +16007,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119548724</v>
+        <v>119548680</v>
       </c>
       <c r="B150" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16019,47 +16019,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480417</v>
+        <v>480609</v>
       </c>
       <c r="R150" t="n">
-        <v>6826298</v>
+        <v>6826134</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16118,10 +16109,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119549018</v>
+        <v>119548676</v>
       </c>
       <c r="B151" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16134,21 +16125,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16158,10 +16149,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480657</v>
+        <v>480460</v>
       </c>
       <c r="R151" t="n">
-        <v>6826051</v>
+        <v>6826167</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16220,10 +16211,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119549020</v>
+        <v>119548741</v>
       </c>
       <c r="B152" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16236,21 +16227,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16260,10 +16251,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480645</v>
+        <v>480229</v>
       </c>
       <c r="R152" t="n">
-        <v>6826039</v>
+        <v>6826288</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16322,10 +16313,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119548644</v>
+        <v>119548981</v>
       </c>
       <c r="B153" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16334,38 +16325,47 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480584</v>
+        <v>480644</v>
       </c>
       <c r="R153" t="n">
-        <v>6826096</v>
+        <v>6826039</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119548638</v>
+        <v>119548775</v>
       </c>
       <c r="B154" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480579</v>
+        <v>480259</v>
       </c>
       <c r="R154" t="n">
-        <v>6826099</v>
+        <v>6826389</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16526,10 +16526,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119549033</v>
+        <v>119548749</v>
       </c>
       <c r="B155" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480552</v>
+        <v>480500</v>
       </c>
       <c r="R155" t="n">
-        <v>6826035</v>
+        <v>6826126</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16628,10 +16628,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119548931</v>
+        <v>119548643</v>
       </c>
       <c r="B156" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16640,47 +16640,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480222</v>
+        <v>480599</v>
       </c>
       <c r="R156" t="n">
-        <v>6826323</v>
+        <v>6826114</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16739,7 +16730,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119548775</v>
+        <v>119548778</v>
       </c>
       <c r="B157" t="n">
         <v>78526</v>
@@ -16779,10 +16770,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480259</v>
+        <v>480271</v>
       </c>
       <c r="R157" t="n">
-        <v>6826389</v>
+        <v>6826362</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16841,10 +16832,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119548685</v>
+        <v>119548976</v>
       </c>
       <c r="B158" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16853,38 +16844,47 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480579</v>
+        <v>480358</v>
       </c>
       <c r="R158" t="n">
-        <v>6826019</v>
+        <v>6826256</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -4391,10 +4391,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119548763</v>
+        <v>119549022</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480302</v>
+        <v>480612</v>
       </c>
       <c r="R37" t="n">
-        <v>6826281</v>
+        <v>6826012</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119548689</v>
+        <v>119548777</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480563</v>
+        <v>480260</v>
       </c>
       <c r="R38" t="n">
-        <v>6826040</v>
+        <v>6826367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119548684</v>
+        <v>119548921</v>
       </c>
       <c r="B39" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480648</v>
+        <v>480627</v>
       </c>
       <c r="R39" t="n">
-        <v>6826037</v>
+        <v>6826045</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119548740</v>
+        <v>119548689</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,21 +4713,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480405</v>
+        <v>480563</v>
       </c>
       <c r="R40" t="n">
-        <v>6826234</v>
+        <v>6826040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119549022</v>
+        <v>119548684</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4815,21 +4815,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480612</v>
+        <v>480648</v>
       </c>
       <c r="R41" t="n">
-        <v>6826012</v>
+        <v>6826037</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119548777</v>
+        <v>119548740</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480260</v>
+        <v>480405</v>
       </c>
       <c r="R42" t="n">
-        <v>6826367</v>
+        <v>6826234</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119548921</v>
+        <v>119548763</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480627</v>
+        <v>480302</v>
       </c>
       <c r="R43" t="n">
-        <v>6826045</v>
+        <v>6826281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,10 +5105,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119548648</v>
+        <v>119548910</v>
       </c>
       <c r="B44" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480609</v>
+        <v>480590</v>
       </c>
       <c r="R44" t="n">
-        <v>6826065</v>
+        <v>6826131</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,10 +5207,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119548599</v>
+        <v>119548771</v>
       </c>
       <c r="B45" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5223,21 +5223,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480302</v>
+        <v>480219</v>
       </c>
       <c r="R45" t="n">
-        <v>6826343</v>
+        <v>6826332</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119549020</v>
+        <v>119548980</v>
       </c>
       <c r="B46" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5321,38 +5321,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480645</v>
+        <v>480624</v>
       </c>
       <c r="R46" t="n">
-        <v>6826039</v>
+        <v>6826016</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,10 +5420,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119549018</v>
+        <v>119548648</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5427,21 +5436,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5451,10 +5460,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480657</v>
+        <v>480609</v>
       </c>
       <c r="R47" t="n">
-        <v>6826051</v>
+        <v>6826065</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5513,10 +5522,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119548910</v>
+        <v>119548599</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5529,21 +5538,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5553,10 +5562,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480590</v>
+        <v>480302</v>
       </c>
       <c r="R48" t="n">
-        <v>6826131</v>
+        <v>6826343</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5615,10 +5624,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119548771</v>
+        <v>119549020</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5631,21 +5640,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5655,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480219</v>
+        <v>480645</v>
       </c>
       <c r="R49" t="n">
-        <v>6826332</v>
+        <v>6826039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5717,10 +5726,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119548980</v>
+        <v>119549018</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5729,47 +5738,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480624</v>
+        <v>480657</v>
       </c>
       <c r="R50" t="n">
-        <v>6826016</v>
+        <v>6826051</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119548737</v>
+        <v>119548638</v>
       </c>
       <c r="B51" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,21 +5844,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480500</v>
+        <v>480579</v>
       </c>
       <c r="R51" t="n">
-        <v>6826127</v>
+        <v>6826099</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119548638</v>
+        <v>119548597</v>
       </c>
       <c r="B52" t="n">
         <v>78560</v>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480579</v>
+        <v>480202</v>
       </c>
       <c r="R52" t="n">
-        <v>6826099</v>
+        <v>6826368</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119548597</v>
+        <v>119549034</v>
       </c>
       <c r="B53" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480202</v>
+        <v>480553</v>
       </c>
       <c r="R53" t="n">
-        <v>6826368</v>
+        <v>6826047</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119549034</v>
+        <v>119549030</v>
       </c>
       <c r="B54" t="n">
         <v>78171</v>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480553</v>
+        <v>480568</v>
       </c>
       <c r="R54" t="n">
-        <v>6826047</v>
+        <v>6826020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6236,10 +6236,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119549030</v>
+        <v>119548688</v>
       </c>
       <c r="B55" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480568</v>
+        <v>480578</v>
       </c>
       <c r="R55" t="n">
-        <v>6826020</v>
+        <v>6826046</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119548688</v>
+        <v>119548737</v>
       </c>
       <c r="B59" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480578</v>
+        <v>480500</v>
       </c>
       <c r="R59" t="n">
-        <v>6826046</v>
+        <v>6826127</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,10 +6755,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119548686</v>
+        <v>119548760</v>
       </c>
       <c r="B60" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480581</v>
+        <v>480323</v>
       </c>
       <c r="R60" t="n">
-        <v>6826014</v>
+        <v>6826258</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,10 +6857,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119548982</v>
+        <v>119548686</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6869,47 +6869,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480584</v>
+        <v>480581</v>
       </c>
       <c r="R61" t="n">
-        <v>6826037</v>
+        <v>6826014</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6968,7 +6959,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548979</v>
+        <v>119548982</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -7003,7 +6994,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7017,10 +7008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480603</v>
+        <v>480584</v>
       </c>
       <c r="R62" t="n">
-        <v>6826118</v>
+        <v>6826037</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7079,10 +7070,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548714</v>
+        <v>119548979</v>
       </c>
       <c r="B63" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7091,38 +7082,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480294</v>
+        <v>480603</v>
       </c>
       <c r="R63" t="n">
-        <v>6826358</v>
+        <v>6826118</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7181,10 +7181,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548776</v>
+        <v>119548714</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7197,21 +7197,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480250</v>
+        <v>480294</v>
       </c>
       <c r="R64" t="n">
-        <v>6826379</v>
+        <v>6826358</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7283,7 +7283,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548760</v>
+        <v>119548776</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480323</v>
+        <v>480250</v>
       </c>
       <c r="R65" t="n">
-        <v>6826258</v>
+        <v>6826379</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7895,10 +7895,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119548772</v>
+        <v>119548596</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7911,21 +7911,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480202</v>
+        <v>480220</v>
       </c>
       <c r="R71" t="n">
-        <v>6826368</v>
+        <v>6826344</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119548682</v>
+        <v>119548598</v>
       </c>
       <c r="B72" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8013,21 +8013,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480635</v>
+        <v>480260</v>
       </c>
       <c r="R72" t="n">
-        <v>6826107</v>
+        <v>6826367</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119548937</v>
+        <v>119548764</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8111,47 +8111,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480612</v>
+        <v>480294</v>
       </c>
       <c r="R73" t="n">
-        <v>6826127</v>
+        <v>6826287</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8201,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119548959</v>
+        <v>119548682</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8222,47 +8213,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480651</v>
+        <v>480635</v>
       </c>
       <c r="R74" t="n">
-        <v>6826110</v>
+        <v>6826107</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8321,10 +8303,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119548596</v>
+        <v>119548772</v>
       </c>
       <c r="B75" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8337,21 +8319,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8361,10 +8343,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480220</v>
+        <v>480202</v>
       </c>
       <c r="R75" t="n">
-        <v>6826344</v>
+        <v>6826368</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8423,10 +8405,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119548598</v>
+        <v>119548651</v>
       </c>
       <c r="B76" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8439,21 +8421,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8463,10 +8445,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480260</v>
+        <v>480424</v>
       </c>
       <c r="R76" t="n">
-        <v>6826367</v>
+        <v>6826300</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8525,10 +8507,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119548764</v>
+        <v>119548937</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8537,38 +8519,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480294</v>
+        <v>480612</v>
       </c>
       <c r="R77" t="n">
-        <v>6826287</v>
+        <v>6826127</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8627,10 +8618,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119548651</v>
+        <v>119548959</v>
       </c>
       <c r="B78" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8639,38 +8630,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480424</v>
+        <v>480651</v>
       </c>
       <c r="R78" t="n">
-        <v>6826300</v>
+        <v>6826110</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119549026</v>
+        <v>119548639</v>
       </c>
       <c r="B79" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8745,21 +8745,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480579</v>
+        <v>480587</v>
       </c>
       <c r="R79" t="n">
-        <v>6826019</v>
+        <v>6826137</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548639</v>
+        <v>119548649</v>
       </c>
       <c r="B80" t="n">
         <v>78560</v>
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480587</v>
+        <v>480632</v>
       </c>
       <c r="R80" t="n">
-        <v>6826137</v>
+        <v>6826029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8933,10 +8933,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119548649</v>
+        <v>119549035</v>
       </c>
       <c r="B81" t="n">
-        <v>78560</v>
+        <v>91832</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8949,21 +8949,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480632</v>
+        <v>480275</v>
       </c>
       <c r="R81" t="n">
-        <v>6826029</v>
+        <v>6826360</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9035,10 +9035,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119549035</v>
+        <v>119548711</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9051,34 +9051,43 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480275</v>
+        <v>480252</v>
       </c>
       <c r="R82" t="n">
-        <v>6826360</v>
+        <v>6826381</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9341,10 +9350,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119548711</v>
+        <v>119549026</v>
       </c>
       <c r="B85" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9357,43 +9366,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480252</v>
+        <v>480579</v>
       </c>
       <c r="R85" t="n">
-        <v>6826381</v>
+        <v>6826019</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10064,10 +10064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548591</v>
+        <v>119548751</v>
       </c>
       <c r="B92" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10080,21 +10080,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480351</v>
+        <v>480657</v>
       </c>
       <c r="R92" t="n">
-        <v>6826254</v>
+        <v>6826036</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10166,10 +10166,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119548751</v>
+        <v>119548591</v>
       </c>
       <c r="B93" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10182,21 +10182,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480657</v>
+        <v>480351</v>
       </c>
       <c r="R93" t="n">
-        <v>6826036</v>
+        <v>6826254</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119549031</v>
+        <v>119548681</v>
       </c>
       <c r="B97" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480572</v>
+        <v>480634</v>
       </c>
       <c r="R97" t="n">
-        <v>6826019</v>
+        <v>6826136</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119548681</v>
+        <v>119548679</v>
       </c>
       <c r="B98" t="n">
         <v>79144</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480634</v>
+        <v>480541</v>
       </c>
       <c r="R98" t="n">
-        <v>6826136</v>
+        <v>6826087</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119548679</v>
+        <v>119549031</v>
       </c>
       <c r="B99" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10794,21 +10794,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480541</v>
+        <v>480572</v>
       </c>
       <c r="R99" t="n">
-        <v>6826087</v>
+        <v>6826019</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11492,10 +11492,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119548973</v>
+        <v>119548779</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11504,25 +11504,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480617</v>
+        <v>480282</v>
       </c>
       <c r="R106" t="n">
-        <v>6826130</v>
+        <v>6826360</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548779</v>
+        <v>119548924</v>
       </c>
       <c r="B107" t="n">
         <v>78526</v>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480282</v>
+        <v>480630</v>
       </c>
       <c r="R107" t="n">
-        <v>6826360</v>
+        <v>6826048</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11696,7 +11696,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548924</v>
+        <v>119548912</v>
       </c>
       <c r="B108" t="n">
         <v>78526</v>
@@ -11736,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480630</v>
+        <v>480641</v>
       </c>
       <c r="R108" t="n">
-        <v>6826048</v>
+        <v>6826128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11798,10 +11798,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548912</v>
+        <v>119548973</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11810,25 +11810,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480641</v>
+        <v>480617</v>
       </c>
       <c r="R109" t="n">
-        <v>6826128</v>
+        <v>6826130</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13337,10 +13337,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119549038</v>
+        <v>119548774</v>
       </c>
       <c r="B124" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480584</v>
+        <v>480232</v>
       </c>
       <c r="R124" t="n">
-        <v>6826087</v>
+        <v>6826378</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119548752</v>
+        <v>119548690</v>
       </c>
       <c r="B125" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13455,21 +13455,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480634</v>
+        <v>480543</v>
       </c>
       <c r="R125" t="n">
-        <v>6826136</v>
+        <v>6826055</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548690</v>
+        <v>119548728</v>
       </c>
       <c r="B126" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13553,25 +13553,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13581,10 +13581,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480543</v>
+        <v>480559</v>
       </c>
       <c r="R126" t="n">
-        <v>6826055</v>
+        <v>6826033</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13643,10 +13643,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119548677</v>
+        <v>119549038</v>
       </c>
       <c r="B127" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13659,21 +13659,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480500</v>
+        <v>480584</v>
       </c>
       <c r="R127" t="n">
-        <v>6826126</v>
+        <v>6826087</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13745,10 +13745,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548728</v>
+        <v>119548752</v>
       </c>
       <c r="B128" t="n">
-        <v>91852</v>
+        <v>78262</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13757,25 +13757,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13785,10 +13785,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480559</v>
+        <v>480634</v>
       </c>
       <c r="R128" t="n">
-        <v>6826033</v>
+        <v>6826136</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13847,10 +13847,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548774</v>
+        <v>119548677</v>
       </c>
       <c r="B129" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13863,21 +13863,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480232</v>
+        <v>480500</v>
       </c>
       <c r="R129" t="n">
-        <v>6826378</v>
+        <v>6826126</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13949,10 +13949,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119548706</v>
+        <v>119548769</v>
       </c>
       <c r="B130" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13965,21 +13965,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13989,10 +13989,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480635</v>
+        <v>480226</v>
       </c>
       <c r="R130" t="n">
-        <v>6826136</v>
+        <v>6826321</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14051,10 +14051,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119548928</v>
+        <v>119548685</v>
       </c>
       <c r="B131" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14067,21 +14067,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14091,10 +14091,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480563</v>
+        <v>480579</v>
       </c>
       <c r="R131" t="n">
-        <v>6826040</v>
+        <v>6826019</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14153,10 +14153,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119549023</v>
+        <v>119548974</v>
       </c>
       <c r="B132" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14165,38 +14165,47 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480611</v>
+        <v>480211</v>
       </c>
       <c r="R132" t="n">
-        <v>6826011</v>
+        <v>6826353</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14255,10 +14264,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548985</v>
+        <v>119548729</v>
       </c>
       <c r="B133" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14267,25 +14276,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14295,10 +14304,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480393</v>
+        <v>480546</v>
       </c>
       <c r="R133" t="n">
-        <v>6826311</v>
+        <v>6826055</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14357,10 +14366,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548713</v>
+        <v>119548722</v>
       </c>
       <c r="B134" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14369,38 +14378,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480232</v>
+        <v>480236</v>
       </c>
       <c r="R134" t="n">
-        <v>6826379</v>
+        <v>6826375</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14459,10 +14477,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119548909</v>
+        <v>119548636</v>
       </c>
       <c r="B135" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14475,21 +14493,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14499,10 +14517,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480580</v>
+        <v>480537</v>
       </c>
       <c r="R135" t="n">
-        <v>6826101</v>
+        <v>6826085</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14561,10 +14579,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119548685</v>
+        <v>119548928</v>
       </c>
       <c r="B136" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14577,21 +14595,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14601,10 +14619,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480579</v>
+        <v>480563</v>
       </c>
       <c r="R136" t="n">
-        <v>6826019</v>
+        <v>6826040</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14663,10 +14681,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119548974</v>
+        <v>119548985</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14675,47 +14693,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480211</v>
+        <v>480393</v>
       </c>
       <c r="R137" t="n">
-        <v>6826353</v>
+        <v>6826311</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14774,10 +14783,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119548729</v>
+        <v>119548713</v>
       </c>
       <c r="B138" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14786,25 +14795,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14814,10 +14823,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480546</v>
+        <v>480232</v>
       </c>
       <c r="R138" t="n">
-        <v>6826055</v>
+        <v>6826379</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14876,10 +14885,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119548722</v>
+        <v>119548909</v>
       </c>
       <c r="B139" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14888,47 +14897,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480236</v>
+        <v>480580</v>
       </c>
       <c r="R139" t="n">
-        <v>6826375</v>
+        <v>6826101</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14987,10 +14987,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119548636</v>
+        <v>119548706</v>
       </c>
       <c r="B140" t="n">
-        <v>78560</v>
+        <v>57463</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15003,21 +15003,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15027,10 +15027,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480537</v>
+        <v>480635</v>
       </c>
       <c r="R140" t="n">
-        <v>6826085</v>
+        <v>6826136</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119548769</v>
+        <v>119549023</v>
       </c>
       <c r="B141" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15105,21 +15105,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480226</v>
+        <v>480611</v>
       </c>
       <c r="R141" t="n">
-        <v>6826321</v>
+        <v>6826011</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119548775</v>
+        <v>119548643</v>
       </c>
       <c r="B154" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480259</v>
+        <v>480599</v>
       </c>
       <c r="R154" t="n">
-        <v>6826389</v>
+        <v>6826114</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16526,10 +16526,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119548749</v>
+        <v>119548778</v>
       </c>
       <c r="B155" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480500</v>
+        <v>480271</v>
       </c>
       <c r="R155" t="n">
-        <v>6826126</v>
+        <v>6826362</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16628,10 +16628,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119548643</v>
+        <v>119548775</v>
       </c>
       <c r="B156" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16644,21 +16644,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480599</v>
+        <v>480259</v>
       </c>
       <c r="R156" t="n">
-        <v>6826114</v>
+        <v>6826389</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16730,10 +16730,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119548778</v>
+        <v>119548976</v>
       </c>
       <c r="B157" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16742,38 +16742,47 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480271</v>
+        <v>480358</v>
       </c>
       <c r="R157" t="n">
-        <v>6826362</v>
+        <v>6826256</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16832,10 +16841,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119548976</v>
+        <v>119548749</v>
       </c>
       <c r="B158" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16844,47 +16853,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480358</v>
+        <v>480500</v>
       </c>
       <c r="R158" t="n">
-        <v>6826256</v>
+        <v>6826126</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -3344,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119549016</v>
+        <v>119548642</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480508</v>
+        <v>480660</v>
       </c>
       <c r="R27" t="n">
-        <v>6826102</v>
+        <v>6826105</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119548948</v>
+        <v>119548679</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,47 +3458,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480229</v>
+        <v>480541</v>
       </c>
       <c r="R28" t="n">
-        <v>6826382</v>
+        <v>6826087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,10 +3548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119548983</v>
+        <v>119548778</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,25 +3560,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3597,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480586</v>
+        <v>480271</v>
       </c>
       <c r="R29" t="n">
-        <v>6826020</v>
+        <v>6826362</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3659,7 +3650,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119548915</v>
+        <v>119548764</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3699,10 +3690,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480639</v>
+        <v>480294</v>
       </c>
       <c r="R30" t="n">
-        <v>6826111</v>
+        <v>6826287</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119548765</v>
+        <v>119549016</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480273</v>
+        <v>480508</v>
       </c>
       <c r="R31" t="n">
-        <v>6826297</v>
+        <v>6826102</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3863,10 +3854,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119548590</v>
+        <v>119548769</v>
       </c>
       <c r="B32" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,21 +3870,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3903,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480405</v>
+        <v>480226</v>
       </c>
       <c r="R32" t="n">
-        <v>6826236</v>
+        <v>6826321</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3956,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119548986</v>
+        <v>119548758</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,21 +3972,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4005,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480423</v>
+        <v>480401</v>
       </c>
       <c r="R33" t="n">
-        <v>6826303</v>
+        <v>6826229</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,10 +4058,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119548932</v>
+        <v>119548924</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4079,47 +4070,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480205</v>
+        <v>480630</v>
       </c>
       <c r="R34" t="n">
-        <v>6826355</v>
+        <v>6826048</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,10 +4160,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119548724</v>
+        <v>119548776</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4190,47 +4172,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480417</v>
+        <v>480250</v>
       </c>
       <c r="R35" t="n">
-        <v>6826298</v>
+        <v>6826379</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119548642</v>
+        <v>119548697</v>
       </c>
       <c r="B36" t="n">
-        <v>78560</v>
+        <v>89633</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,21 +4278,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4329,10 +4302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480660</v>
+        <v>480557</v>
       </c>
       <c r="R36" t="n">
-        <v>6826105</v>
+        <v>6826036</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4391,10 +4364,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119549022</v>
+        <v>119548643</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,21 +4380,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4431,10 +4404,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480612</v>
+        <v>480599</v>
       </c>
       <c r="R37" t="n">
-        <v>6826012</v>
+        <v>6826114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,10 +4466,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119548777</v>
+        <v>119549027</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4509,21 +4482,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4533,10 +4506,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480260</v>
+        <v>480581</v>
       </c>
       <c r="R38" t="n">
-        <v>6826367</v>
+        <v>6826018</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,10 +4568,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119548921</v>
+        <v>119548749</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4611,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4635,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480627</v>
+        <v>480500</v>
       </c>
       <c r="R39" t="n">
-        <v>6826045</v>
+        <v>6826126</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4697,7 +4670,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119548689</v>
+        <v>119548688</v>
       </c>
       <c r="B40" t="n">
         <v>79144</v>
@@ -4737,10 +4710,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480563</v>
+        <v>480578</v>
       </c>
       <c r="R40" t="n">
-        <v>6826040</v>
+        <v>6826046</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4799,10 +4772,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119548684</v>
+        <v>119548768</v>
       </c>
       <c r="B41" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4815,21 +4788,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4839,10 +4812,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480648</v>
+        <v>480257</v>
       </c>
       <c r="R41" t="n">
-        <v>6826037</v>
+        <v>6826287</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,10 +4874,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119548740</v>
+        <v>119548718</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4917,21 +4890,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4941,10 +4914,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480405</v>
+        <v>480637</v>
       </c>
       <c r="R42" t="n">
-        <v>6826234</v>
+        <v>6826047</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5003,10 +4976,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119548763</v>
+        <v>119549034</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5019,21 +4992,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5043,10 +5016,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480302</v>
+        <v>480553</v>
       </c>
       <c r="R43" t="n">
-        <v>6826281</v>
+        <v>6826047</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,10 +5078,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119548910</v>
+        <v>119548645</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5121,21 +5094,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5145,10 +5118,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480590</v>
+        <v>480584</v>
       </c>
       <c r="R44" t="n">
-        <v>6826131</v>
+        <v>6826087</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,10 +5180,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119548771</v>
+        <v>119548599</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5223,21 +5196,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5247,10 +5220,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480219</v>
+        <v>480302</v>
       </c>
       <c r="R45" t="n">
-        <v>6826332</v>
+        <v>6826343</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,7 +5282,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119548980</v>
+        <v>119548937</v>
       </c>
       <c r="B46" t="n">
         <v>91840</v>
@@ -5358,10 +5331,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480624</v>
+        <v>480612</v>
       </c>
       <c r="R46" t="n">
-        <v>6826016</v>
+        <v>6826127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5420,10 +5393,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119548648</v>
+        <v>119548743</v>
       </c>
       <c r="B47" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5436,21 +5409,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5460,10 +5433,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480609</v>
+        <v>480578</v>
       </c>
       <c r="R47" t="n">
-        <v>6826065</v>
+        <v>6826046</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5522,10 +5495,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119548599</v>
+        <v>119548690</v>
       </c>
       <c r="B48" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5538,21 +5511,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5562,10 +5535,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480302</v>
+        <v>480543</v>
       </c>
       <c r="R48" t="n">
-        <v>6826343</v>
+        <v>6826055</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5624,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119549020</v>
+        <v>119548680</v>
       </c>
       <c r="B49" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5640,21 +5613,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5664,10 +5637,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480645</v>
+        <v>480609</v>
       </c>
       <c r="R49" t="n">
-        <v>6826039</v>
+        <v>6826134</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5726,10 +5699,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119549018</v>
+        <v>119548685</v>
       </c>
       <c r="B50" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5742,21 +5715,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5766,10 +5739,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480657</v>
+        <v>480579</v>
       </c>
       <c r="R50" t="n">
-        <v>6826051</v>
+        <v>6826019</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5828,7 +5801,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119548638</v>
+        <v>119548595</v>
       </c>
       <c r="B51" t="n">
         <v>78560</v>
@@ -5868,10 +5841,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480579</v>
+        <v>480235</v>
       </c>
       <c r="R51" t="n">
-        <v>6826099</v>
+        <v>6826296</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5930,10 +5903,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119548597</v>
+        <v>119548696</v>
       </c>
       <c r="B52" t="n">
-        <v>78560</v>
+        <v>79115</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5946,21 +5919,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5970,10 +5943,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480202</v>
+        <v>480493</v>
       </c>
       <c r="R52" t="n">
-        <v>6826368</v>
+        <v>6826131</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6032,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119549034</v>
+        <v>119548775</v>
       </c>
       <c r="B53" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6048,21 +6021,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6072,10 +6045,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480553</v>
+        <v>480259</v>
       </c>
       <c r="R53" t="n">
-        <v>6826047</v>
+        <v>6826389</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6134,10 +6107,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119549030</v>
+        <v>119548774</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6150,21 +6123,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6174,10 +6147,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480568</v>
+        <v>480232</v>
       </c>
       <c r="R54" t="n">
-        <v>6826020</v>
+        <v>6826378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6236,10 +6209,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119548688</v>
+        <v>119548979</v>
       </c>
       <c r="B55" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6248,38 +6221,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480578</v>
+        <v>480603</v>
       </c>
       <c r="R55" t="n">
-        <v>6826046</v>
+        <v>6826118</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6338,10 +6320,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119548691</v>
+        <v>119548982</v>
       </c>
       <c r="B56" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6350,38 +6332,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480539</v>
+        <v>480584</v>
       </c>
       <c r="R56" t="n">
-        <v>6826061</v>
+        <v>6826037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6440,7 +6431,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119548931</v>
+        <v>119548974</v>
       </c>
       <c r="B57" t="n">
         <v>91840</v>
@@ -6489,10 +6480,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480222</v>
+        <v>480211</v>
       </c>
       <c r="R57" t="n">
-        <v>6826323</v>
+        <v>6826353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6551,10 +6542,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119548759</v>
+        <v>119549020</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6567,21 +6558,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6591,10 +6582,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480354</v>
+        <v>480645</v>
       </c>
       <c r="R58" t="n">
-        <v>6826256</v>
+        <v>6826039</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,10 +6644,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119548737</v>
+        <v>119548598</v>
       </c>
       <c r="B59" t="n">
-        <v>78263</v>
+        <v>78560</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6669,21 +6660,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6693,10 +6684,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480500</v>
+        <v>480260</v>
       </c>
       <c r="R59" t="n">
-        <v>6826127</v>
+        <v>6826367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6746,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119548760</v>
+        <v>119548925</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -6795,10 +6786,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480323</v>
+        <v>480632</v>
       </c>
       <c r="R60" t="n">
-        <v>6826258</v>
+        <v>6826030</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,10 +6848,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119548686</v>
+        <v>119548637</v>
       </c>
       <c r="B61" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6873,21 +6864,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6897,10 +6888,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480581</v>
+        <v>480555</v>
       </c>
       <c r="R61" t="n">
-        <v>6826014</v>
+        <v>6826106</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6959,10 +6950,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119548982</v>
+        <v>119548986</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6971,47 +6962,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480584</v>
+        <v>480423</v>
       </c>
       <c r="R62" t="n">
-        <v>6826037</v>
+        <v>6826303</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7070,10 +7052,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119548979</v>
+        <v>119548722</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7086,26 +7068,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7119,10 +7101,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480603</v>
+        <v>480236</v>
       </c>
       <c r="R63" t="n">
-        <v>6826118</v>
+        <v>6826375</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7181,10 +7163,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119548714</v>
+        <v>119548763</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7197,21 +7179,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7221,10 +7203,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480294</v>
+        <v>480302</v>
       </c>
       <c r="R64" t="n">
-        <v>6826358</v>
+        <v>6826281</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7283,7 +7265,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119548776</v>
+        <v>119548916</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7323,10 +7305,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480250</v>
+        <v>480586</v>
       </c>
       <c r="R65" t="n">
-        <v>6826379</v>
+        <v>6826085</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7385,10 +7367,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119548744</v>
+        <v>119548639</v>
       </c>
       <c r="B66" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7401,21 +7383,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7425,10 +7407,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480408</v>
+        <v>480587</v>
       </c>
       <c r="R66" t="n">
-        <v>6826259</v>
+        <v>6826137</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7487,7 +7469,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119548687</v>
+        <v>119548650</v>
       </c>
       <c r="B67" t="n">
         <v>79144</v>
@@ -7527,10 +7509,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480571</v>
+        <v>480226</v>
       </c>
       <c r="R67" t="n">
-        <v>6826019</v>
+        <v>6826322</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7589,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119549024</v>
+        <v>119548752</v>
       </c>
       <c r="B68" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7605,21 +7587,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7629,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480607</v>
+        <v>480634</v>
       </c>
       <c r="R68" t="n">
-        <v>6826012</v>
+        <v>6826136</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7691,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119548770</v>
+        <v>119548678</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7707,21 +7689,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7731,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480222</v>
+        <v>480510</v>
       </c>
       <c r="R69" t="n">
-        <v>6826323</v>
+        <v>6826101</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7793,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119548913</v>
+        <v>119548682</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7809,21 +7791,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7833,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480660</v>
+        <v>480635</v>
       </c>
       <c r="R70" t="n">
-        <v>6826105</v>
+        <v>6826107</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7895,10 +7877,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119548596</v>
+        <v>119548760</v>
       </c>
       <c r="B71" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7911,21 +7893,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7935,10 +7917,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480220</v>
+        <v>480323</v>
       </c>
       <c r="R71" t="n">
-        <v>6826344</v>
+        <v>6826258</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7997,10 +7979,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119548598</v>
+        <v>119548711</v>
       </c>
       <c r="B72" t="n">
-        <v>78560</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8013,34 +7995,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480260</v>
+        <v>480252</v>
       </c>
       <c r="R72" t="n">
-        <v>6826367</v>
+        <v>6826381</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8099,10 +8090,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119548764</v>
+        <v>119548739</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8115,21 +8106,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8139,10 +8130,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480294</v>
+        <v>480598</v>
       </c>
       <c r="R73" t="n">
-        <v>6826287</v>
+        <v>6826021</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8201,10 +8192,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119548682</v>
+        <v>119549019</v>
       </c>
       <c r="B74" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8217,21 +8208,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8241,10 +8232,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480635</v>
+        <v>480650</v>
       </c>
       <c r="R74" t="n">
-        <v>6826107</v>
+        <v>6826031</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8303,10 +8294,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119548772</v>
+        <v>119549026</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8319,21 +8310,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8343,10 +8334,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480202</v>
+        <v>480579</v>
       </c>
       <c r="R75" t="n">
-        <v>6826368</v>
+        <v>6826019</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8405,10 +8396,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119548651</v>
+        <v>119548723</v>
       </c>
       <c r="B76" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8417,38 +8408,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480424</v>
+        <v>480609</v>
       </c>
       <c r="R76" t="n">
-        <v>6826300</v>
+        <v>6826134</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119548937</v>
+        <v>119548973</v>
       </c>
       <c r="B77" t="n">
         <v>91840</v>
@@ -8540,26 +8540,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480612</v>
+        <v>480617</v>
       </c>
       <c r="R77" t="n">
-        <v>6826127</v>
+        <v>6826130</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8618,10 +8609,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119548959</v>
+        <v>119548744</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8630,47 +8621,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480651</v>
+        <v>480408</v>
       </c>
       <c r="R78" t="n">
-        <v>6826110</v>
+        <v>6826259</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8729,10 +8711,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119548639</v>
+        <v>119548684</v>
       </c>
       <c r="B79" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8745,21 +8727,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8769,10 +8751,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480587</v>
+        <v>480648</v>
       </c>
       <c r="R79" t="n">
-        <v>6826137</v>
+        <v>6826037</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8831,10 +8813,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119548649</v>
+        <v>119548588</v>
       </c>
       <c r="B80" t="n">
-        <v>78560</v>
+        <v>74638</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8847,21 +8829,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8871,10 +8853,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480632</v>
+        <v>480240</v>
       </c>
       <c r="R80" t="n">
-        <v>6826029</v>
+        <v>6826296</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8933,10 +8915,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119549035</v>
+        <v>119548770</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8949,21 +8931,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8973,10 +8955,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>480275</v>
+        <v>480222</v>
       </c>
       <c r="R81" t="n">
-        <v>6826360</v>
+        <v>6826323</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9035,10 +9017,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119548711</v>
+        <v>119548922</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9051,43 +9033,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480252</v>
+        <v>480630</v>
       </c>
       <c r="R82" t="n">
-        <v>6826381</v>
+        <v>6826050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9146,10 +9119,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119549033</v>
+        <v>119548912</v>
       </c>
       <c r="B83" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9162,21 +9135,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9186,10 +9159,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480552</v>
+        <v>480641</v>
       </c>
       <c r="R83" t="n">
-        <v>6826035</v>
+        <v>6826128</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9248,10 +9221,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119549019</v>
+        <v>119548948</v>
       </c>
       <c r="B84" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9260,38 +9233,47 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480650</v>
+        <v>480229</v>
       </c>
       <c r="R84" t="n">
-        <v>6826031</v>
+        <v>6826382</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9350,10 +9332,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119549026</v>
+        <v>119548728</v>
       </c>
       <c r="B85" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9362,25 +9344,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9390,10 +9372,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480579</v>
+        <v>480559</v>
       </c>
       <c r="R85" t="n">
-        <v>6826019</v>
+        <v>6826033</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9452,7 +9434,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119548914</v>
+        <v>119548777</v>
       </c>
       <c r="B86" t="n">
         <v>78526</v>
@@ -9492,10 +9474,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480642</v>
+        <v>480260</v>
       </c>
       <c r="R86" t="n">
-        <v>6826105</v>
+        <v>6826367</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9554,10 +9536,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119549032</v>
+        <v>119548765</v>
       </c>
       <c r="B87" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9570,21 +9552,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9594,10 +9576,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480575</v>
+        <v>480273</v>
       </c>
       <c r="R87" t="n">
-        <v>6826022</v>
+        <v>6826297</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9656,10 +9638,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119548739</v>
+        <v>119548921</v>
       </c>
       <c r="B88" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9672,21 +9654,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9696,10 +9678,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480598</v>
+        <v>480627</v>
       </c>
       <c r="R88" t="n">
-        <v>6826021</v>
+        <v>6826045</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9758,7 +9740,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119548595</v>
+        <v>119548638</v>
       </c>
       <c r="B89" t="n">
         <v>78560</v>
@@ -9798,10 +9780,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>480235</v>
+        <v>480579</v>
       </c>
       <c r="R89" t="n">
-        <v>6826296</v>
+        <v>6826099</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9860,10 +9842,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119548922</v>
+        <v>119548597</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9876,21 +9858,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9900,10 +9882,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480630</v>
+        <v>480202</v>
       </c>
       <c r="R90" t="n">
-        <v>6826050</v>
+        <v>6826368</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9962,10 +9944,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119548761</v>
+        <v>119549032</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9978,21 +9960,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10002,10 +9984,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480311</v>
+        <v>480575</v>
       </c>
       <c r="R91" t="n">
-        <v>6826268</v>
+        <v>6826022</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10064,10 +10046,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119548751</v>
+        <v>119548636</v>
       </c>
       <c r="B92" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10080,21 +10062,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10104,10 +10086,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>480657</v>
+        <v>480537</v>
       </c>
       <c r="R92" t="n">
-        <v>6826036</v>
+        <v>6826085</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10166,7 +10148,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119548591</v>
+        <v>119548641</v>
       </c>
       <c r="B93" t="n">
         <v>78560</v>
@@ -10206,10 +10188,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480351</v>
+        <v>480602</v>
       </c>
       <c r="R93" t="n">
-        <v>6826254</v>
+        <v>6826129</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10268,10 +10250,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119549029</v>
+        <v>119548681</v>
       </c>
       <c r="B94" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10284,21 +10266,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10308,10 +10290,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480565</v>
+        <v>480634</v>
       </c>
       <c r="R94" t="n">
-        <v>6826017</v>
+        <v>6826136</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10370,10 +10352,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119548758</v>
+        <v>119548689</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10386,21 +10368,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10410,10 +10392,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480401</v>
+        <v>480563</v>
       </c>
       <c r="R95" t="n">
-        <v>6826229</v>
+        <v>6826040</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,10 +10454,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119548768</v>
+        <v>119549018</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10488,21 +10470,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10512,10 +10494,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480257</v>
+        <v>480657</v>
       </c>
       <c r="R96" t="n">
-        <v>6826287</v>
+        <v>6826051</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,10 +10556,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119548681</v>
+        <v>119549025</v>
       </c>
       <c r="B97" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10590,21 +10572,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10614,10 +10596,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>480634</v>
+        <v>480604</v>
       </c>
       <c r="R97" t="n">
-        <v>6826136</v>
+        <v>6826016</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,10 +10658,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119548679</v>
+        <v>119548594</v>
       </c>
       <c r="B98" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10692,21 +10674,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10716,10 +10698,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480541</v>
+        <v>480261</v>
       </c>
       <c r="R98" t="n">
-        <v>6826087</v>
+        <v>6826289</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10760,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119549031</v>
+        <v>119548649</v>
       </c>
       <c r="B99" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10794,21 +10776,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10800,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>480572</v>
+        <v>480632</v>
       </c>
       <c r="R99" t="n">
-        <v>6826019</v>
+        <v>6826029</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,10 +10862,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119548718</v>
+        <v>119548976</v>
       </c>
       <c r="B100" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10892,38 +10874,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480637</v>
+        <v>480358</v>
       </c>
       <c r="R100" t="n">
-        <v>6826047</v>
+        <v>6826256</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10982,10 +10973,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119548697</v>
+        <v>119549035</v>
       </c>
       <c r="B101" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10998,21 +10989,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11022,10 +11013,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480557</v>
+        <v>480275</v>
       </c>
       <c r="R101" t="n">
-        <v>6826036</v>
+        <v>6826360</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11084,10 +11075,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119549021</v>
+        <v>119548959</v>
       </c>
       <c r="B102" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11096,38 +11087,47 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>480634</v>
+        <v>480651</v>
       </c>
       <c r="R102" t="n">
-        <v>6826019</v>
+        <v>6826110</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119549025</v>
+        <v>119548737</v>
       </c>
       <c r="B103" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11202,21 +11202,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>480604</v>
+        <v>480500</v>
       </c>
       <c r="R103" t="n">
-        <v>6826016</v>
+        <v>6826127</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119548745</v>
+        <v>119548741</v>
       </c>
       <c r="B104" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11304,21 +11304,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11328,10 +11328,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>480226</v>
+        <v>480229</v>
       </c>
       <c r="R104" t="n">
-        <v>6826322</v>
+        <v>6826288</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11390,10 +11390,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119548675</v>
+        <v>119548914</v>
       </c>
       <c r="B105" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11406,21 +11406,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480451</v>
+        <v>480642</v>
       </c>
       <c r="R105" t="n">
-        <v>6826172</v>
+        <v>6826105</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119548779</v>
+        <v>119548772</v>
       </c>
       <c r="B106" t="n">
         <v>78526</v>
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480282</v>
+        <v>480202</v>
       </c>
       <c r="R106" t="n">
-        <v>6826360</v>
+        <v>6826368</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11594,10 +11594,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119548924</v>
+        <v>119548706</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11610,21 +11610,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>480630</v>
+        <v>480635</v>
       </c>
       <c r="R107" t="n">
-        <v>6826048</v>
+        <v>6826136</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11696,10 +11696,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119548912</v>
+        <v>119548730</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11712,21 +11712,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11736,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480641</v>
+        <v>480608</v>
       </c>
       <c r="R108" t="n">
-        <v>6826128</v>
+        <v>6826130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11798,10 +11798,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119548973</v>
+        <v>119548651</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11810,25 +11810,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480617</v>
+        <v>480424</v>
       </c>
       <c r="R109" t="n">
-        <v>6826130</v>
+        <v>6826300</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11900,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119548723</v>
+        <v>119548909</v>
       </c>
       <c r="B110" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11912,47 +11912,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480609</v>
+        <v>480580</v>
       </c>
       <c r="R110" t="n">
-        <v>6826134</v>
+        <v>6826101</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12011,7 +12002,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119549027</v>
+        <v>119549023</v>
       </c>
       <c r="B111" t="n">
         <v>78171</v>
@@ -12051,10 +12042,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480581</v>
+        <v>480611</v>
       </c>
       <c r="R111" t="n">
-        <v>6826018</v>
+        <v>6826011</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12113,7 +12104,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119548637</v>
+        <v>119548596</v>
       </c>
       <c r="B112" t="n">
         <v>78560</v>
@@ -12153,10 +12144,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480555</v>
+        <v>480220</v>
       </c>
       <c r="R112" t="n">
-        <v>6826106</v>
+        <v>6826344</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12215,10 +12206,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119548589</v>
+        <v>119549024</v>
       </c>
       <c r="B113" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12231,21 +12222,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12255,10 +12246,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480414</v>
+        <v>480607</v>
       </c>
       <c r="R113" t="n">
-        <v>6826211</v>
+        <v>6826012</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12317,10 +12308,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119548587</v>
+        <v>119549021</v>
       </c>
       <c r="B114" t="n">
-        <v>91836</v>
+        <v>78171</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12329,25 +12320,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4363</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12357,10 +12348,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480252</v>
+        <v>480634</v>
       </c>
       <c r="R114" t="n">
-        <v>6826381</v>
+        <v>6826019</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12419,10 +12410,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119548916</v>
+        <v>119548644</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12435,21 +12426,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12459,10 +12450,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>480586</v>
+        <v>480584</v>
       </c>
       <c r="R115" t="n">
-        <v>6826085</v>
+        <v>6826096</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12521,10 +12512,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119548730</v>
+        <v>119549031</v>
       </c>
       <c r="B116" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,21 +12528,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12561,10 +12552,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>480608</v>
+        <v>480572</v>
       </c>
       <c r="R116" t="n">
-        <v>6826130</v>
+        <v>6826019</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12623,10 +12614,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119548762</v>
+        <v>119548932</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12635,38 +12626,47 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480309</v>
+        <v>480205</v>
       </c>
       <c r="R117" t="n">
-        <v>6826277</v>
+        <v>6826355</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12725,10 +12725,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119548640</v>
+        <v>119548587</v>
       </c>
       <c r="B118" t="n">
-        <v>78560</v>
+        <v>91836</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>4363</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480602</v>
+        <v>480252</v>
       </c>
       <c r="R118" t="n">
-        <v>6826132</v>
+        <v>6826381</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12827,10 +12827,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119548594</v>
+        <v>119549029</v>
       </c>
       <c r="B119" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,21 +12843,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12867,10 +12867,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>480261</v>
+        <v>480565</v>
       </c>
       <c r="R119" t="n">
-        <v>6826289</v>
+        <v>6826017</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12929,10 +12929,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119548911</v>
+        <v>119548928</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12945,21 +12945,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>480588</v>
+        <v>480563</v>
       </c>
       <c r="R120" t="n">
-        <v>6826137</v>
+        <v>6826040</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13031,10 +13031,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119548925</v>
+        <v>119548590</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13047,21 +13047,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480632</v>
+        <v>480405</v>
       </c>
       <c r="R121" t="n">
-        <v>6826030</v>
+        <v>6826236</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13133,10 +13133,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119548743</v>
+        <v>119549033</v>
       </c>
       <c r="B122" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,21 +13149,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480578</v>
+        <v>480552</v>
       </c>
       <c r="R122" t="n">
-        <v>6826046</v>
+        <v>6826035</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13235,10 +13235,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119548696</v>
+        <v>119548981</v>
       </c>
       <c r="B123" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13247,38 +13247,47 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480493</v>
+        <v>480644</v>
       </c>
       <c r="R123" t="n">
-        <v>6826131</v>
+        <v>6826039</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13337,10 +13346,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119548774</v>
+        <v>119548729</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13349,25 +13358,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13377,10 +13386,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480232</v>
+        <v>480546</v>
       </c>
       <c r="R124" t="n">
-        <v>6826378</v>
+        <v>6826055</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13439,10 +13448,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119548690</v>
+        <v>119548751</v>
       </c>
       <c r="B125" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13455,21 +13464,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13479,10 +13488,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480543</v>
+        <v>480657</v>
       </c>
       <c r="R125" t="n">
-        <v>6826055</v>
+        <v>6826036</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13541,10 +13550,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119548728</v>
+        <v>119548676</v>
       </c>
       <c r="B126" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13553,25 +13562,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13581,10 +13590,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>480559</v>
+        <v>480460</v>
       </c>
       <c r="R126" t="n">
-        <v>6826033</v>
+        <v>6826167</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13643,10 +13652,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119549038</v>
+        <v>119548915</v>
       </c>
       <c r="B127" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13659,21 +13668,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13683,10 +13692,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480584</v>
+        <v>480639</v>
       </c>
       <c r="R127" t="n">
-        <v>6826087</v>
+        <v>6826111</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13745,10 +13754,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119548752</v>
+        <v>119548767</v>
       </c>
       <c r="B128" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13761,21 +13770,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13785,10 +13794,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480634</v>
+        <v>480266</v>
       </c>
       <c r="R128" t="n">
-        <v>6826136</v>
+        <v>6826294</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13847,10 +13856,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119548677</v>
+        <v>119548761</v>
       </c>
       <c r="B129" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13863,21 +13872,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13887,10 +13896,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>480500</v>
+        <v>480311</v>
       </c>
       <c r="R129" t="n">
-        <v>6826126</v>
+        <v>6826268</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13949,7 +13958,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119548769</v>
+        <v>119548759</v>
       </c>
       <c r="B130" t="n">
         <v>78526</v>
@@ -13989,10 +13998,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480226</v>
+        <v>480354</v>
       </c>
       <c r="R130" t="n">
-        <v>6826321</v>
+        <v>6826256</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14051,10 +14060,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119548685</v>
+        <v>119548910</v>
       </c>
       <c r="B131" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14067,21 +14076,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14091,10 +14100,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480579</v>
+        <v>480590</v>
       </c>
       <c r="R131" t="n">
-        <v>6826019</v>
+        <v>6826131</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14153,10 +14162,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119548974</v>
+        <v>119548589</v>
       </c>
       <c r="B132" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14165,47 +14174,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480211</v>
+        <v>480414</v>
       </c>
       <c r="R132" t="n">
-        <v>6826353</v>
+        <v>6826211</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14264,7 +14264,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119548729</v>
+        <v>119548724</v>
       </c>
       <c r="B133" t="n">
         <v>91852</v>
@@ -14297,17 +14297,26 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>480546</v>
+        <v>480417</v>
       </c>
       <c r="R133" t="n">
-        <v>6826055</v>
+        <v>6826298</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14366,10 +14375,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119548722</v>
+        <v>119548677</v>
       </c>
       <c r="B134" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14378,47 +14387,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480236</v>
+        <v>480500</v>
       </c>
       <c r="R134" t="n">
-        <v>6826375</v>
+        <v>6826126</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14477,10 +14477,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119548636</v>
+        <v>119548675</v>
       </c>
       <c r="B135" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14493,21 +14493,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480537</v>
+        <v>480451</v>
       </c>
       <c r="R135" t="n">
-        <v>6826085</v>
+        <v>6826172</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14579,7 +14579,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119548928</v>
+        <v>119549030</v>
       </c>
       <c r="B136" t="n">
         <v>78171</v>
@@ -14619,10 +14619,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480563</v>
+        <v>480568</v>
       </c>
       <c r="R136" t="n">
-        <v>6826040</v>
+        <v>6826020</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14681,10 +14681,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119548985</v>
+        <v>119548635</v>
       </c>
       <c r="B137" t="n">
-        <v>78171</v>
+        <v>78560</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14697,21 +14697,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14721,10 +14721,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480393</v>
+        <v>480439</v>
       </c>
       <c r="R137" t="n">
-        <v>6826311</v>
+        <v>6826220</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14783,10 +14783,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119548713</v>
+        <v>119548931</v>
       </c>
       <c r="B138" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14795,38 +14795,47 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480232</v>
+        <v>480222</v>
       </c>
       <c r="R138" t="n">
-        <v>6826379</v>
+        <v>6826323</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14885,10 +14894,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119548909</v>
+        <v>119548714</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14901,21 +14910,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14925,10 +14934,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480580</v>
+        <v>480294</v>
       </c>
       <c r="R139" t="n">
-        <v>6826101</v>
+        <v>6826358</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14987,10 +14996,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119548706</v>
+        <v>119548762</v>
       </c>
       <c r="B140" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15003,21 +15012,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15027,10 +15036,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480635</v>
+        <v>480309</v>
       </c>
       <c r="R140" t="n">
-        <v>6826136</v>
+        <v>6826277</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15089,10 +15098,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119549023</v>
+        <v>119548687</v>
       </c>
       <c r="B141" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15105,21 +15114,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15129,10 +15138,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>480611</v>
+        <v>480571</v>
       </c>
       <c r="R141" t="n">
-        <v>6826011</v>
+        <v>6826019</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15191,10 +15200,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119548767</v>
+        <v>119548691</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15207,21 +15216,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15231,10 +15240,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>480266</v>
+        <v>480539</v>
       </c>
       <c r="R142" t="n">
-        <v>6826294</v>
+        <v>6826061</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15293,10 +15302,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119548588</v>
+        <v>119548983</v>
       </c>
       <c r="B143" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15305,25 +15314,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15333,10 +15342,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>480240</v>
+        <v>480586</v>
       </c>
       <c r="R143" t="n">
-        <v>6826296</v>
+        <v>6826020</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15395,10 +15404,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119548650</v>
+        <v>119548980</v>
       </c>
       <c r="B144" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15407,38 +15416,47 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>480226</v>
+        <v>480624</v>
       </c>
       <c r="R144" t="n">
-        <v>6826322</v>
+        <v>6826016</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15497,7 +15515,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119548644</v>
+        <v>119548591</v>
       </c>
       <c r="B145" t="n">
         <v>78560</v>
@@ -15537,10 +15555,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>480584</v>
+        <v>480351</v>
       </c>
       <c r="R145" t="n">
-        <v>6826096</v>
+        <v>6826254</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15599,7 +15617,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119548635</v>
+        <v>119548648</v>
       </c>
       <c r="B146" t="n">
         <v>78560</v>
@@ -15639,10 +15657,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>480439</v>
+        <v>480609</v>
       </c>
       <c r="R146" t="n">
-        <v>6826220</v>
+        <v>6826065</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15701,10 +15719,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119548641</v>
+        <v>119548686</v>
       </c>
       <c r="B147" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15717,21 +15735,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15741,10 +15759,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>480602</v>
+        <v>480581</v>
       </c>
       <c r="R147" t="n">
-        <v>6826129</v>
+        <v>6826014</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,10 +15821,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119548593</v>
+        <v>119548740</v>
       </c>
       <c r="B148" t="n">
-        <v>78560</v>
+        <v>79607</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15819,21 +15837,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15843,10 +15861,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480302</v>
+        <v>480405</v>
       </c>
       <c r="R148" t="n">
-        <v>6826281</v>
+        <v>6826234</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15905,10 +15923,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119548678</v>
+        <v>119548771</v>
       </c>
       <c r="B149" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15921,21 +15939,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15945,10 +15963,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480510</v>
+        <v>480219</v>
       </c>
       <c r="R149" t="n">
-        <v>6826101</v>
+        <v>6826332</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16007,10 +16025,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119548680</v>
+        <v>119548779</v>
       </c>
       <c r="B150" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16023,21 +16041,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16047,10 +16065,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>480609</v>
+        <v>480282</v>
       </c>
       <c r="R150" t="n">
-        <v>6826134</v>
+        <v>6826360</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16109,10 +16127,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119548676</v>
+        <v>119548713</v>
       </c>
       <c r="B151" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16125,21 +16143,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16149,10 +16167,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480460</v>
+        <v>480232</v>
       </c>
       <c r="R151" t="n">
-        <v>6826167</v>
+        <v>6826379</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16211,10 +16229,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119548741</v>
+        <v>119548913</v>
       </c>
       <c r="B152" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16227,21 +16245,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16251,10 +16269,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>480229</v>
+        <v>480660</v>
       </c>
       <c r="R152" t="n">
-        <v>6826288</v>
+        <v>6826105</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16313,10 +16331,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119548981</v>
+        <v>119548640</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16325,47 +16343,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>480644</v>
+        <v>480602</v>
       </c>
       <c r="R153" t="n">
-        <v>6826039</v>
+        <v>6826132</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16424,10 +16433,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119548643</v>
+        <v>119548985</v>
       </c>
       <c r="B154" t="n">
-        <v>78560</v>
+        <v>78171</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16440,21 +16449,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16464,10 +16473,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>480599</v>
+        <v>480393</v>
       </c>
       <c r="R154" t="n">
-        <v>6826114</v>
+        <v>6826311</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16526,10 +16535,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119548778</v>
+        <v>119549022</v>
       </c>
       <c r="B155" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16542,21 +16551,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16566,10 +16575,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480271</v>
+        <v>480612</v>
       </c>
       <c r="R155" t="n">
-        <v>6826362</v>
+        <v>6826012</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16628,10 +16637,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119548775</v>
+        <v>119548593</v>
       </c>
       <c r="B156" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16644,21 +16653,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16668,10 +16677,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480259</v>
+        <v>480302</v>
       </c>
       <c r="R156" t="n">
-        <v>6826389</v>
+        <v>6826281</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16730,10 +16739,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119548976</v>
+        <v>119548745</v>
       </c>
       <c r="B157" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16742,47 +16751,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Strömparterren, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480358</v>
+        <v>480226</v>
       </c>
       <c r="R157" t="n">
-        <v>6826256</v>
+        <v>6826322</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16841,10 +16841,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119548749</v>
+        <v>119548911</v>
       </c>
       <c r="B158" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16857,21 +16857,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16881,10 +16881,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480500</v>
+        <v>480588</v>
       </c>
       <c r="R158" t="n">
-        <v>6826126</v>
+        <v>6826137</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>119228098</v>
       </c>
       <c r="B11" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>119228098</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 30505-2024 artfynd.xlsx
+++ b/artfynd/A 30505-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AZ168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548590</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548591</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548594</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548595</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548596</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548597</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548599</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548633</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548635</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548636</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548637</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548638</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548639</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548640</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548641</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548642</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548643</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548644</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548645</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548646</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548647</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548648</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3801,6 +3961,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548649</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3902,6 +4067,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228123</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3999,6 +4169,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548928</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548984</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4193,6 +4373,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548985</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4290,6 +4475,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548986</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4387,6 +4577,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549016</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4484,6 +4679,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549018</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4581,6 +4781,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549019</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4678,6 +4883,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549020</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4775,6 +4985,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549021</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4872,6 +5087,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549022</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4969,6 +5189,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549023</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5066,6 +5291,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549024</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5163,6 +5393,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5260,6 +5495,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549026</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5357,6 +5597,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549027</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5454,6 +5699,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549029</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5551,6 +5801,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549030</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5648,6 +5903,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549031</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5745,6 +6005,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549032</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5842,6 +6107,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549033</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5939,6 +6209,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549034</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6040,6 +6315,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227874</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6141,6 +6421,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228118</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6238,6 +6523,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548697</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6335,6 +6625,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548730</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6436,6 +6731,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227891</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6533,6 +6833,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549035</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6630,6 +6935,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548587</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6731,6 +7041,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227886</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6832,6 +7147,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228011</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6938,6 +7258,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548931</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7044,6 +7369,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548932</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7150,6 +7480,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548937</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7256,6 +7591,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548948</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7362,6 +7702,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548959</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7459,6 +7804,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548973</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7565,6 +7915,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548974</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7671,6 +8026,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548976</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7777,6 +8137,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548979</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7883,6 +8248,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548980</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7989,6 +8359,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548981</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8095,6 +8470,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548982</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8192,6 +8572,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548983</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8298,6 +8683,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548722</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8404,6 +8794,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548723</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8510,6 +8905,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548724</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8607,6 +9007,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548728</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8704,6 +9109,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548729</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8805,6 +9215,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227901</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8911,6 +9326,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227939</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9012,6 +9432,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228005</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9118,6 +9543,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228056</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9219,6 +9649,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228067</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9316,6 +9751,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548758</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9413,6 +9853,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548759</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9510,6 +9955,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548760</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9607,6 +10057,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548761</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9704,6 +10159,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548762</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9801,6 +10261,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548763</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9898,6 +10363,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548764</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9995,6 +10465,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548765</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10092,6 +10567,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548767</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10189,6 +10669,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548768</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10286,6 +10771,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548769</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10383,6 +10873,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548770</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10480,6 +10975,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548771</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10577,6 +11077,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548772</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10674,6 +11179,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548774</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10771,6 +11281,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548775</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10868,6 +11383,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548776</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10965,6 +11485,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548777</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11062,6 +11587,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548778</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11159,6 +11689,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548779</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11256,6 +11791,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548780</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11353,6 +11893,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548909</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11450,6 +11995,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548910</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11547,6 +12097,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548911</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11644,6 +12199,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548912</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11741,6 +12301,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548913</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11838,6 +12403,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548914</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11935,6 +12505,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548915</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12032,6 +12607,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548916</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12129,6 +12709,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548917</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12226,6 +12811,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548918</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12323,6 +12913,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548920</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12420,6 +13015,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548921</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12517,6 +13117,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548922</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12614,6 +13219,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548924</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12711,6 +13321,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548925</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12808,6 +13423,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548588</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12905,6 +13525,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548743</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13002,6 +13627,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548744</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13099,6 +13729,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548745</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13196,6 +13831,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548749</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13293,6 +13933,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548750</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13390,6 +14035,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548751</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13487,6 +14137,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548752</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13588,6 +14243,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228044</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13685,6 +14345,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548650</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13782,6 +14447,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548651</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13879,6 +14549,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548674</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13976,6 +14651,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548675</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14073,6 +14753,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548676</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14170,6 +14855,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548677</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14267,6 +14957,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548678</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14364,6 +15059,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548679</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14461,6 +15161,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548680</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14558,6 +15263,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548681</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14655,6 +15365,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548682</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14752,6 +15467,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548683</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14849,6 +15569,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548684</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14946,6 +15671,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548685</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15043,6 +15773,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548686</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15140,6 +15875,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548687</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15237,6 +15977,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548688</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15334,6 +16079,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548689</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15431,6 +16181,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548690</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15528,6 +16283,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548691</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15629,6 +16389,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228063</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15726,6 +16491,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548740</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15823,6 +16593,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548741</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15924,6 +16699,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228070</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16029,6 +16809,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228098</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16126,6 +16911,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548754</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16223,6 +17013,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548706</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16324,6 +17119,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227917</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16425,6 +17225,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227949</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16526,6 +17331,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227964</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16627,6 +17437,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119227981</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16728,6 +17543,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228042</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16825,6 +17645,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548737</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16922,6 +17747,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548739</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17023,6 +17853,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119228035</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17120,8 +17955,182 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119548696</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>